--- a/ERP使用情况-01.xlsx
+++ b/ERP使用情况-01.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14040"/>
+    <workbookView windowWidth="29400" windowHeight="14040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="职能部门ERP操作汇总" sheetId="4" r:id="rId1"/>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>高</t>
     </r>
     <r>
@@ -419,6 +425,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>杨</t>
     </r>
     <r>
@@ -451,6 +463,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>李</t>
     </r>
     <r>
@@ -7182,7 +7200,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -7210,13 +7228,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7561,36 +7573,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
@@ -7601,32 +7613,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B2)</f>
         <v>6</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>4</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B2,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>65</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B2,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>4230</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B2)</f>
         <v>1946295</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B2)</f>
         <v>28</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B2)</f>
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <f t="shared" ref="A3:A16" si="0">ROW()-1</f>
         <v>2</v>
       </c>
@@ -7637,32 +7649,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B3)</f>
         <v>15</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>6</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B3,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>121</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B3,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>965</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B3)</f>
         <v>913705</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B3)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B3)</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -7673,32 +7685,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B4)</f>
         <v>10</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>10</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B4,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>44</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B4,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>40026</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B4)</f>
         <v>25164981</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B4)</f>
         <v>721</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B4)</f>
         <v>1011</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -7709,32 +7721,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B5)</f>
         <v>10</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>10</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B5,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>61</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B5,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>1929</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B5)</f>
         <v>565947</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B5)</f>
         <v>11</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B5)</f>
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -7745,32 +7757,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B6)</f>
         <v>8</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>7</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B6,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>2837</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B6,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>26889</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B6)</f>
         <v>73769892</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B6)</f>
         <v>1427</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B6)</f>
         <v>8501</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -7781,32 +7793,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B7)</f>
         <v>10</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>9</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B7,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>48</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B7,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>3544</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B7)</f>
         <v>1752929</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B7)</f>
         <v>330</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B7)</f>
         <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -7817,32 +7829,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B8)</f>
         <v>23</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>14</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B8,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>656</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B8,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>4272</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B8)</f>
         <v>21581216</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B8)</f>
         <v>174</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B8)</f>
         <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -7853,32 +7865,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B9)</f>
         <v>7</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>7</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B9,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>484</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B9,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>8890</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B9)</f>
         <v>7670723</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B9)</f>
         <v>233</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B9)</f>
         <v>717</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -7889,32 +7901,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B10)</f>
         <v>2</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B10,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>61</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B10,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>9704</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B10)</f>
         <v>3089524</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B10)</f>
         <v>178</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B10)</f>
         <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -7925,32 +7937,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B11)</f>
         <v>22</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>14</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B11,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>252</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B11,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>12115</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B11)</f>
         <v>3537751</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B11)</f>
         <v>84</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B11)</f>
         <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -7961,32 +7973,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B12)</f>
         <v>11</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>11</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B12,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>738</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B12,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>18608</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B12)</f>
         <v>10887835</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B12)</f>
         <v>1178</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B12)</f>
         <v>1745</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -7997,32 +8009,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B13)</f>
         <v>30</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>22</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B13,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>885</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B13,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>14424</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B13)</f>
         <v>5310149</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B13)</f>
         <v>621</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B13)</f>
         <v>1261</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -8033,32 +8045,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B14)</f>
         <v>9</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>9</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B14,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>501</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B14,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>5947</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B14)</f>
         <v>11876366</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B14)</f>
         <v>334</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B14)</f>
         <v>1519</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -8069,32 +8081,32 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B15)</f>
         <v>25</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>25</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B15,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>3334</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B15,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>133779</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B15)</f>
         <v>422719875</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B15)</f>
         <v>2853</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B15)</f>
         <v>4048</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -8105,61 +8117,61 @@
         <f>COUNTIFS(职能部门人员台账!A:A,B16)</f>
         <v>20</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>10</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B16,职能部门人员ERP操作!D:D,"发起者")</f>
         <v>207</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <f>SUMIFS(职能部门人员ERP操作!E:E,职能部门人员ERP操作!A:A,B16,职能部门人员ERP操作!D:D,"*审批*")</f>
         <v>10855</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <f>SUMIFS(职能部门人员ERP操作!F:F,职能部门人员ERP操作!A:A,B16)</f>
         <v>144947571</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <f>SUMIFS(职能部门人员ERP操作!G:G,职能部门人员ERP操作!A:A,B16)</f>
         <v>70</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <f>SUMIFS(职能部门人员ERP操作!H:H,职能部门人员ERP操作!A:A,B16)</f>
         <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="11">
-        <f>SUM(C2:C16)</f>
+      <c r="C17" s="10">
+        <f t="shared" ref="C17:I17" si="1">SUM(C2:C16)</f>
         <v>208</v>
       </c>
-      <c r="D17" s="11">
-        <f>SUM(D2:D16)</f>
+      <c r="D17" s="10">
+        <f t="shared" si="1"/>
         <v>159</v>
       </c>
-      <c r="E17" s="11">
-        <f>SUM(E2:E16)</f>
+      <c r="E17" s="10">
+        <f t="shared" si="1"/>
         <v>10294</v>
       </c>
-      <c r="F17" s="11">
-        <f>SUM(F2:F16)</f>
+      <c r="F17" s="10">
+        <f t="shared" si="1"/>
         <v>296177</v>
       </c>
-      <c r="G17" s="11">
-        <f>SUM(G2:G16)</f>
+      <c r="G17" s="10">
+        <f t="shared" si="1"/>
         <v>735734759</v>
       </c>
-      <c r="H17" s="11">
-        <f>SUM(H2:H16)</f>
+      <c r="H17" s="10">
+        <f t="shared" si="1"/>
         <v>8243</v>
       </c>
-      <c r="I17" s="11">
-        <f>SUM(I2:I16)</f>
+      <c r="I17" s="10">
+        <f t="shared" si="1"/>
         <v>20734</v>
       </c>
     </row>
@@ -8218,16 +8230,16 @@
       <c r="D2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <v>24</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>6374</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8244,16 +8256,16 @@
       <c r="D3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>5</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>588</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>0</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>1</v>
       </c>
     </row>
@@ -8270,16 +8282,16 @@
       <c r="D4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>3405</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>1331324</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>21</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>28</v>
       </c>
     </row>
@@ -8296,16 +8308,16 @@
       <c r="D5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>21</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>1219</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>0</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8322,16 +8334,16 @@
       <c r="D6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>653</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>511612</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>7</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>10</v>
       </c>
     </row>
@@ -8348,16 +8360,16 @@
       <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>37</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>23671</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>0</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>1</v>
       </c>
     </row>
@@ -8374,16 +8386,16 @@
       <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>148</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>63111</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>0</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8400,16 +8412,16 @@
       <c r="D9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>2</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>8396</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>0</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8426,16 +8438,16 @@
       <c r="D10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>179</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8452,16 +8464,16 @@
       <c r="D11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>345</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>5961</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8478,16 +8490,16 @@
       <c r="D12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>100</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>9</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>0</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8504,16 +8516,16 @@
       <c r="D13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <v>27</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>23557</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>0</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8530,16 +8542,16 @@
       <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <v>8</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>19</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>0</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8556,16 +8568,16 @@
       <c r="D15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>19</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>59413</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>1</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>1</v>
       </c>
     </row>
@@ -8582,16 +8594,16 @@
       <c r="D16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>11</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>594</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>0</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8608,16 +8620,16 @@
       <c r="D17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>568</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>823909</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>0</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8634,16 +8646,16 @@
       <c r="D18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>4</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>56</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8660,16 +8672,16 @@
       <c r="D19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>2</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>0</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>1</v>
       </c>
     </row>
@@ -8686,16 +8698,16 @@
       <c r="D20" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <v>2164</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>1553398</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>13</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>16</v>
       </c>
     </row>
@@ -8712,16 +8724,16 @@
       <c r="D21" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <v>9081</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>3254174</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>152</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>211</v>
       </c>
     </row>
@@ -8738,16 +8750,16 @@
       <c r="D22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>10</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>1726</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>0</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8764,16 +8776,16 @@
       <c r="D23" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <v>2453</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>1412398</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>4</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <v>11</v>
       </c>
     </row>
@@ -8790,16 +8802,16 @@
       <c r="D24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="8">
         <v>2</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="8">
         <v>358</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8816,16 +8828,16 @@
       <c r="D25" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="8">
         <v>3309</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="8">
         <v>693992</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="8">
         <v>15</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <v>56</v>
       </c>
     </row>
@@ -8842,16 +8854,16 @@
       <c r="D26" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="8">
         <v>25</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="8">
         <v>20</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="8">
         <v>0</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="8">
         <v>2</v>
       </c>
     </row>
@@ -8868,16 +8880,16 @@
       <c r="D27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <v>3836</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <v>3802126</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="8">
         <v>16</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <v>117</v>
       </c>
     </row>
@@ -8894,16 +8906,16 @@
       <c r="D28" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="8">
         <v>599</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="8">
         <v>278209</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8">
         <v>0</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8920,16 +8932,16 @@
       <c r="D29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>3189</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>2666576</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <v>465</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>519</v>
       </c>
     </row>
@@ -8946,16 +8958,16 @@
       <c r="D30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="8">
         <v>5</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="8">
         <v>22608</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="8">
         <v>0</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="8">
         <v>4</v>
       </c>
     </row>
@@ -8972,16 +8984,16 @@
       <c r="D31" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="8">
         <v>5313</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <v>6566753</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <v>26</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <v>36</v>
       </c>
     </row>
@@ -8998,16 +9010,16 @@
       <c r="D32" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <v>2</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="8">
         <v>0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="8">
         <v>0</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9024,16 +9036,16 @@
       <c r="D33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="8">
         <v>7198</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="8">
         <v>4199845</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="8">
         <v>29</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="8">
         <v>37</v>
       </c>
     </row>
@@ -9050,16 +9062,16 @@
       <c r="D34" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="8">
         <v>2884</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="8">
         <v>712798</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="8">
         <v>1</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="8">
         <v>2</v>
       </c>
     </row>
@@ -9076,16 +9088,16 @@
       <c r="D35" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="8">
         <v>12</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="8">
         <v>2919</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="8">
         <v>0</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9102,16 +9114,16 @@
       <c r="D36" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="8">
         <v>16</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="8">
         <v>72889</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="8">
         <v>0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9128,16 +9140,16 @@
       <c r="D37" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="8">
         <v>5</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="8">
         <v>8800</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="8">
         <v>0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <v>1</v>
       </c>
     </row>
@@ -9154,16 +9166,16 @@
       <c r="D38" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="8">
         <v>21</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="8">
         <v>2088</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="8">
         <v>2</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="8">
         <v>3</v>
       </c>
     </row>
@@ -9180,16 +9192,16 @@
       <c r="D39" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="8">
         <v>52</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="8">
         <v>4020</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="8">
         <v>3</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="8">
         <v>7</v>
       </c>
     </row>
@@ -9206,16 +9218,16 @@
       <c r="D40" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="8">
         <v>8</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="8">
         <v>418</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="8">
         <v>0</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9232,16 +9244,16 @@
       <c r="D41" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="8">
         <v>2</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="8">
         <v>26</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="8">
         <v>0</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9258,16 +9270,16 @@
       <c r="D42" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="8">
         <v>12</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="8">
         <v>10060</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="8">
         <v>0</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="8">
         <v>5</v>
       </c>
     </row>
@@ -9284,16 +9296,16 @@
       <c r="D43" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="8">
         <v>1</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="8">
         <v>1</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="8">
         <v>0</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9310,16 +9322,16 @@
       <c r="D44" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="8">
         <v>13</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="8">
         <v>10306</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="8">
         <v>0</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9336,16 +9348,16 @@
       <c r="D45" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="8">
         <v>1829</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="8">
         <v>449286</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="8">
         <v>6</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="8">
         <v>16</v>
       </c>
     </row>
@@ -9362,16 +9374,16 @@
       <c r="D46" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="8">
         <v>11</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="8">
         <v>265</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="8">
         <v>0</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9388,16 +9400,16 @@
       <c r="D47" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="8">
         <v>6</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="8">
         <v>1026</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="8">
         <v>0</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="8">
         <v>2</v>
       </c>
     </row>
@@ -9414,16 +9426,16 @@
       <c r="D48" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="8">
         <v>2</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="8">
         <v>3843</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="8">
         <v>0</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9440,16 +9452,16 @@
       <c r="D49" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="8">
         <v>2056</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="8">
         <v>766770</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="8">
         <v>103</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="8">
         <v>219</v>
       </c>
     </row>
@@ -9466,16 +9478,16 @@
       <c r="D50" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="8">
         <v>63</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="8">
         <v>524266</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="8">
         <v>0</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="8">
         <v>13</v>
       </c>
     </row>
@@ -9492,16 +9504,16 @@
       <c r="D51" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="8">
         <v>160</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="8">
         <v>203072</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="8">
         <v>1</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="8">
         <v>9</v>
       </c>
     </row>
@@ -9518,16 +9530,16 @@
       <c r="D52" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="8">
         <v>107</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="8">
         <v>107000</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="8">
         <v>0</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="8">
         <v>32</v>
       </c>
     </row>
@@ -9544,16 +9556,16 @@
       <c r="D53" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="8">
         <v>25</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="8">
         <v>91041</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="8">
         <v>0</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9570,16 +9582,16 @@
       <c r="D54" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="8">
         <v>8269</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="8">
         <v>58438817</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="8">
         <v>755</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="8">
         <v>5220</v>
       </c>
     </row>
@@ -9596,16 +9608,16 @@
       <c r="D55" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="8">
         <v>83</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="8">
         <v>110907</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="8">
         <v>0</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="8">
         <v>34</v>
       </c>
     </row>
@@ -9622,16 +9634,16 @@
       <c r="D56" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="8">
         <v>849</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="8">
         <v>9041301</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="8">
         <v>135</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="8">
         <v>208</v>
       </c>
     </row>
@@ -9648,16 +9660,16 @@
       <c r="D57" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="8">
         <v>99</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="8">
         <v>9898</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="8">
         <v>0</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="8">
         <v>32</v>
       </c>
     </row>
@@ -9674,16 +9686,16 @@
       <c r="D58" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="8">
         <v>15300</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="8">
         <v>3452297</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="8">
         <v>412</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="8">
         <v>2608</v>
       </c>
     </row>
@@ -9700,16 +9712,16 @@
       <c r="D59" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="8">
         <v>2481</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="8">
         <v>11332</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="8">
         <v>0</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="8">
         <v>68</v>
       </c>
     </row>
@@ -9726,16 +9738,16 @@
       <c r="D60" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="8">
         <v>230</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="8">
         <v>1011022</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="8">
         <v>21</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="8">
         <v>57</v>
       </c>
     </row>
@@ -9752,16 +9764,16 @@
       <c r="D61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="8">
         <v>4</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="8">
         <v>2169</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="8">
         <v>0</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61" s="8">
         <v>1</v>
       </c>
     </row>
@@ -9778,16 +9790,16 @@
       <c r="D62" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="8">
         <v>1623</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="8">
         <v>717206</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="8">
         <v>9</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="8">
         <v>50</v>
       </c>
     </row>
@@ -9804,16 +9816,16 @@
       <c r="D63" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="8">
         <v>10</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="8">
         <v>12</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="8">
         <v>0</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="8">
         <v>1</v>
       </c>
     </row>
@@ -9830,16 +9842,16 @@
       <c r="D64" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="8">
         <v>1067</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="8">
         <v>401395</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="8">
         <v>189</v>
       </c>
-      <c r="H64" s="9">
+      <c r="H64" s="8">
         <v>221</v>
       </c>
     </row>
@@ -9856,16 +9868,16 @@
       <c r="D65" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="8">
         <v>7</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="8">
         <v>328</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65" s="8">
         <v>0</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9882,16 +9894,16 @@
       <c r="D66" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="8">
         <v>2</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66" s="8">
         <v>15</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66" s="8">
         <v>0</v>
       </c>
-      <c r="H66" s="9">
+      <c r="H66" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9908,16 +9920,16 @@
       <c r="D67" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E67" s="8">
         <v>239</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67" s="8">
         <v>147415</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67" s="8">
         <v>0</v>
       </c>
-      <c r="H67" s="9">
+      <c r="H67" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9934,16 +9946,16 @@
       <c r="D68" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="8">
         <v>67</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="8">
         <v>15901</v>
       </c>
-      <c r="G68" s="9">
+      <c r="G68" s="8">
         <v>4</v>
       </c>
-      <c r="H68" s="9">
+      <c r="H68" s="8">
         <v>4</v>
       </c>
     </row>
@@ -9960,16 +9972,16 @@
       <c r="D69" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E69" s="9">
+      <c r="E69" s="8">
         <v>4</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="8">
         <v>2</v>
       </c>
-      <c r="G69" s="9">
+      <c r="G69" s="8">
         <v>0</v>
       </c>
-      <c r="H69" s="9">
+      <c r="H69" s="8">
         <v>0</v>
       </c>
     </row>
@@ -9986,16 +9998,16 @@
       <c r="D70" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E70" s="9">
+      <c r="E70" s="8">
         <v>4</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F70" s="8">
         <v>447</v>
       </c>
-      <c r="G70" s="9">
+      <c r="G70" s="8">
         <v>0</v>
       </c>
-      <c r="H70" s="9">
+      <c r="H70" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10012,16 +10024,16 @@
       <c r="D71" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E71" s="9">
+      <c r="E71" s="8">
         <v>10</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="8">
         <v>1195</v>
       </c>
-      <c r="G71" s="9">
+      <c r="G71" s="8">
         <v>0</v>
       </c>
-      <c r="H71" s="9">
+      <c r="H71" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10038,16 +10050,16 @@
       <c r="D72" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="8">
         <v>10</v>
       </c>
-      <c r="F72" s="9">
+      <c r="F72" s="8">
         <v>48</v>
       </c>
-      <c r="G72" s="9">
+      <c r="G72" s="8">
         <v>0</v>
       </c>
-      <c r="H72" s="9">
+      <c r="H72" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10064,16 +10076,16 @@
       <c r="D73" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E73" s="9">
+      <c r="E73" s="8">
         <v>535</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="8">
         <v>468431</v>
       </c>
-      <c r="G73" s="9">
+      <c r="G73" s="8">
         <v>128</v>
       </c>
-      <c r="H73" s="9">
+      <c r="H73" s="8">
         <v>131</v>
       </c>
     </row>
@@ -10090,16 +10102,16 @@
       <c r="D74" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="8">
         <v>6</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="8">
         <v>522</v>
       </c>
-      <c r="G74" s="9">
+      <c r="G74" s="8">
         <v>0</v>
       </c>
-      <c r="H74" s="9">
+      <c r="H74" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10116,16 +10128,16 @@
       <c r="D75" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E75" s="9">
+      <c r="E75" s="8">
         <v>3</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="8">
         <v>8</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="8">
         <v>0</v>
       </c>
-      <c r="H75" s="9">
+      <c r="H75" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10142,16 +10154,16 @@
       <c r="D76" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="8">
         <v>5</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="8">
         <v>4</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="8">
         <v>0</v>
       </c>
-      <c r="H76" s="9">
+      <c r="H76" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10168,16 +10180,16 @@
       <c r="D77" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="8">
         <v>64</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="8">
         <v>287647</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="8">
         <v>0</v>
       </c>
-      <c r="H77" s="9">
+      <c r="H77" s="8">
         <v>27</v>
       </c>
     </row>
@@ -10194,16 +10206,16 @@
       <c r="D78" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="8">
         <v>7</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="8">
         <v>11632</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="8">
         <v>0</v>
       </c>
-      <c r="H78" s="9">
+      <c r="H78" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10220,16 +10232,16 @@
       <c r="D79" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E79" s="9">
+      <c r="E79" s="8">
         <v>299</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="8">
         <v>585724</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="8">
         <v>19</v>
       </c>
-      <c r="H79" s="9">
+      <c r="H79" s="8">
         <v>52</v>
       </c>
     </row>
@@ -10246,16 +10258,16 @@
       <c r="D80" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E80" s="9">
+      <c r="E80" s="8">
         <v>250</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="8">
         <v>381110</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="8">
         <v>0</v>
       </c>
-      <c r="H80" s="9">
+      <c r="H80" s="8">
         <v>76</v>
       </c>
     </row>
@@ -10272,16 +10284,16 @@
       <c r="D81" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E81" s="9">
+      <c r="E81" s="8">
         <v>2</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81" s="8">
         <v>11136</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="8">
         <v>0</v>
       </c>
-      <c r="H81" s="9">
+      <c r="H81" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10298,16 +10310,16 @@
       <c r="D82" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="8">
         <v>4</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="8">
         <v>48887</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="8">
         <v>0</v>
       </c>
-      <c r="H82" s="9">
+      <c r="H82" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10324,16 +10336,16 @@
       <c r="D83" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E83" s="9">
+      <c r="E83" s="8">
         <v>32</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="8">
         <v>49780</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="8">
         <v>0</v>
       </c>
-      <c r="H83" s="9">
+      <c r="H83" s="8">
         <v>12</v>
       </c>
     </row>
@@ -10350,16 +10362,16 @@
       <c r="D84" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="8">
         <v>217</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="8">
         <v>366997</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="8">
         <v>14</v>
       </c>
-      <c r="H84" s="9">
+      <c r="H84" s="8">
         <v>12</v>
       </c>
     </row>
@@ -10376,16 +10388,16 @@
       <c r="D85" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="8">
         <v>6</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="8">
         <v>215472</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="8">
         <v>0</v>
       </c>
-      <c r="H85" s="9">
+      <c r="H85" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10402,16 +10414,16 @@
       <c r="D86" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E86" s="9">
+      <c r="E86" s="8">
         <v>12</v>
       </c>
-      <c r="F86" s="9">
+      <c r="F86" s="8">
         <v>7308</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="8">
         <v>1</v>
       </c>
-      <c r="H86" s="9">
+      <c r="H86" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10428,16 +10440,16 @@
       <c r="D87" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="8">
         <v>6</v>
       </c>
-      <c r="F87" s="9">
+      <c r="F87" s="8">
         <v>0</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="8">
         <v>0</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H87" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10454,16 +10466,16 @@
       <c r="D88" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="8">
         <v>5</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="8">
         <v>10883</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="8">
         <v>0</v>
       </c>
-      <c r="H88" s="9">
+      <c r="H88" s="8">
         <v>4</v>
       </c>
     </row>
@@ -10480,16 +10492,16 @@
       <c r="D89" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E89" s="9">
+      <c r="E89" s="8">
         <v>2</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="8">
         <v>145</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="8">
         <v>0</v>
       </c>
-      <c r="H89" s="9">
+      <c r="H89" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10506,16 +10518,16 @@
       <c r="D90" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="8">
         <v>27</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="8">
         <v>3662</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="8">
         <v>0</v>
       </c>
-      <c r="H90" s="9">
+      <c r="H90" s="8">
         <v>2</v>
       </c>
     </row>
@@ -10532,16 +10544,16 @@
       <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="9">
+      <c r="E91" s="8">
         <v>54</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="8">
         <v>54131</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="8">
         <v>0</v>
       </c>
-      <c r="H91" s="9">
+      <c r="H91" s="8">
         <v>27</v>
       </c>
     </row>
@@ -10558,16 +10570,16 @@
       <c r="D92" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="8">
         <v>3100</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="8">
         <v>18462474</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="8">
         <v>129</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H92" s="8">
         <v>190</v>
       </c>
     </row>
@@ -10584,16 +10596,16 @@
       <c r="D93" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="8">
         <v>251</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="8">
         <v>186991</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="8">
         <v>0</v>
       </c>
-      <c r="H93" s="9">
+      <c r="H93" s="8">
         <v>103</v>
       </c>
     </row>
@@ -10610,16 +10622,16 @@
       <c r="D94" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="8">
         <v>457</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="8">
         <v>652871</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="8">
         <v>11</v>
       </c>
-      <c r="H94" s="9">
+      <c r="H94" s="8">
         <v>13</v>
       </c>
     </row>
@@ -10636,16 +10648,16 @@
       <c r="D95" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="8">
         <v>32</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95" s="8">
         <v>110587</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95" s="8">
         <v>0</v>
       </c>
-      <c r="H95" s="9">
+      <c r="H95" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10662,16 +10674,16 @@
       <c r="D96" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="8">
         <v>4</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96" s="8">
         <v>63246</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="8">
         <v>0</v>
       </c>
-      <c r="H96" s="9">
+      <c r="H96" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10688,16 +10700,16 @@
       <c r="D97" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E97" s="9">
+      <c r="E97" s="8">
         <v>8</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="8">
         <v>4127</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97" s="8">
         <v>0</v>
       </c>
-      <c r="H97" s="9">
+      <c r="H97" s="8">
         <v>2</v>
       </c>
     </row>
@@ -10714,16 +10726,16 @@
       <c r="D98" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="8">
         <v>14</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="8">
         <v>33356</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="8">
         <v>0</v>
       </c>
-      <c r="H98" s="9">
+      <c r="H98" s="8">
         <v>2</v>
       </c>
     </row>
@@ -10740,16 +10752,16 @@
       <c r="D99" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E99" s="9">
+      <c r="E99" s="8">
         <v>2</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="8">
         <v>5873</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="8">
         <v>0</v>
       </c>
-      <c r="H99" s="9">
+      <c r="H99" s="8">
         <v>1</v>
       </c>
     </row>
@@ -10766,16 +10778,16 @@
       <c r="D100" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="8">
         <v>73</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="8">
         <v>27177</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="8">
         <v>0</v>
       </c>
-      <c r="H100" s="9">
+      <c r="H100" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10792,16 +10804,16 @@
       <c r="D101" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E101" s="9">
+      <c r="E101" s="8">
         <v>4340</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="8">
         <v>2769223</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="8">
         <v>56</v>
       </c>
-      <c r="H101" s="9">
+      <c r="H101" s="8">
         <v>80</v>
       </c>
     </row>
@@ -10818,16 +10830,16 @@
       <c r="D102" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="8">
         <v>270</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="8">
         <v>14624</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="8">
         <v>0</v>
       </c>
-      <c r="H102" s="9">
+      <c r="H102" s="8">
         <v>26</v>
       </c>
     </row>
@@ -10844,16 +10856,16 @@
       <c r="D103" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="8">
         <v>14</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="8">
         <v>7414</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="8">
         <v>0</v>
       </c>
-      <c r="H103" s="9">
+      <c r="H103" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10870,16 +10882,16 @@
       <c r="D104" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="8">
         <v>20</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="8">
         <v>1704</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="8">
         <v>0</v>
       </c>
-      <c r="H104" s="9">
+      <c r="H104" s="8">
         <v>4</v>
       </c>
     </row>
@@ -10896,16 +10908,16 @@
       <c r="D105" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E105" s="9">
+      <c r="E105" s="8">
         <v>189</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105" s="8">
         <v>972273</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="8">
         <v>3</v>
       </c>
-      <c r="H105" s="9">
+      <c r="H105" s="8">
         <v>3</v>
       </c>
     </row>
@@ -10922,16 +10934,16 @@
       <c r="D106" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E106" s="8">
         <v>98</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="8">
         <v>304797</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="8">
         <v>0</v>
       </c>
-      <c r="H106" s="9">
+      <c r="H106" s="8">
         <v>9</v>
       </c>
     </row>
@@ -10948,16 +10960,16 @@
       <c r="D107" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E107" s="9">
+      <c r="E107" s="8">
         <v>3322</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="8">
         <v>3245233</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="8">
         <v>162</v>
       </c>
-      <c r="H107" s="9">
+      <c r="H107" s="8">
         <v>567</v>
       </c>
     </row>
@@ -10974,16 +10986,16 @@
       <c r="D108" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E108" s="9">
+      <c r="E108" s="8">
         <v>7</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="8">
         <v>19086</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108" s="8">
         <v>0</v>
       </c>
-      <c r="H108" s="9">
+      <c r="H108" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11000,16 +11012,16 @@
       <c r="D109" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E109" s="9">
+      <c r="E109" s="8">
         <v>188</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="8">
         <v>102016</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="8">
         <v>0</v>
       </c>
-      <c r="H109" s="9">
+      <c r="H109" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11026,16 +11038,16 @@
       <c r="D110" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E110" s="9">
+      <c r="E110" s="8">
         <v>62</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="8">
         <v>46715</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="8">
         <v>0</v>
       </c>
-      <c r="H110" s="9">
+      <c r="H110" s="8">
         <v>5</v>
       </c>
     </row>
@@ -11052,16 +11064,16 @@
       <c r="D111" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E111" s="9">
+      <c r="E111" s="8">
         <v>62</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="8">
         <v>41235</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="8">
         <v>0</v>
       </c>
-      <c r="H111" s="9">
+      <c r="H111" s="8">
         <v>1</v>
       </c>
     </row>
@@ -11078,16 +11090,16 @@
       <c r="D112" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E112" s="9">
+      <c r="E112" s="8">
         <v>22</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112" s="8">
         <v>21440</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="8">
         <v>0</v>
       </c>
-      <c r="H112" s="9">
+      <c r="H112" s="8">
         <v>3</v>
       </c>
     </row>
@@ -11104,16 +11116,16 @@
       <c r="D113" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E113" s="9">
+      <c r="E113" s="8">
         <v>775</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="8">
         <v>124961</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113" s="8">
         <v>12</v>
       </c>
-      <c r="H113" s="9">
+      <c r="H113" s="8">
         <v>19</v>
       </c>
     </row>
@@ -11130,16 +11142,16 @@
       <c r="D114" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E114" s="9">
+      <c r="E114" s="8">
         <v>5</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114" s="8">
         <v>2</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="8">
         <v>0</v>
       </c>
-      <c r="H114" s="9">
+      <c r="H114" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11156,16 +11168,16 @@
       <c r="D115" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E115" s="9">
+      <c r="E115" s="8">
         <v>9704</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115" s="8">
         <v>3061393</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="8">
         <v>178</v>
       </c>
-      <c r="H115" s="9">
+      <c r="H115" s="8">
         <v>362</v>
       </c>
     </row>
@@ -11182,16 +11194,16 @@
       <c r="D116" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E116" s="9">
+      <c r="E116" s="8">
         <v>61</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116" s="8">
         <v>28131</v>
       </c>
-      <c r="G116" s="9">
+      <c r="G116" s="8">
         <v>0</v>
       </c>
-      <c r="H116" s="9">
+      <c r="H116" s="8">
         <v>17</v>
       </c>
     </row>
@@ -11208,16 +11220,16 @@
       <c r="D117" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E117" s="9">
+      <c r="E117" s="8">
         <v>4</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117" s="8">
         <v>1668</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117" s="8">
         <v>0</v>
       </c>
-      <c r="H117" s="9">
+      <c r="H117" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11234,16 +11246,16 @@
       <c r="D118" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E118" s="9">
+      <c r="E118" s="8">
         <v>2</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F118" s="8">
         <v>1</v>
       </c>
-      <c r="G118" s="9">
+      <c r="G118" s="8">
         <v>0</v>
       </c>
-      <c r="H118" s="9">
+      <c r="H118" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11260,16 +11272,16 @@
       <c r="D119" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E119" s="9">
+      <c r="E119" s="8">
         <v>4</v>
       </c>
-      <c r="F119" s="9">
+      <c r="F119" s="8">
         <v>44</v>
       </c>
-      <c r="G119" s="9">
+      <c r="G119" s="8">
         <v>0</v>
       </c>
-      <c r="H119" s="9">
+      <c r="H119" s="8">
         <v>1</v>
       </c>
     </row>
@@ -11286,16 +11298,16 @@
       <c r="D120" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E120" s="9">
+      <c r="E120" s="8">
         <v>2648</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F120" s="8">
         <v>1342493</v>
       </c>
-      <c r="G120" s="9">
+      <c r="G120" s="8">
         <v>11</v>
       </c>
-      <c r="H120" s="9">
+      <c r="H120" s="8">
         <v>19</v>
       </c>
     </row>
@@ -11312,16 +11324,16 @@
       <c r="D121" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="9">
+      <c r="E121" s="8">
         <v>65</v>
       </c>
-      <c r="F121" s="9">
+      <c r="F121" s="8">
         <v>9</v>
       </c>
-      <c r="G121" s="9">
+      <c r="G121" s="8">
         <v>0</v>
       </c>
-      <c r="H121" s="9">
+      <c r="H121" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11338,16 +11350,16 @@
       <c r="D122" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E122" s="9">
+      <c r="E122" s="8">
         <v>7</v>
       </c>
-      <c r="F122" s="9">
+      <c r="F122" s="8">
         <v>24</v>
       </c>
-      <c r="G122" s="9">
+      <c r="G122" s="8">
         <v>0</v>
       </c>
-      <c r="H122" s="9">
+      <c r="H122" s="8">
         <v>4</v>
       </c>
     </row>
@@ -11364,16 +11376,16 @@
       <c r="D123" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E123" s="9">
+      <c r="E123" s="8">
         <v>2</v>
       </c>
-      <c r="F123" s="9">
+      <c r="F123" s="8">
         <v>960</v>
       </c>
-      <c r="G123" s="9">
+      <c r="G123" s="8">
         <v>0</v>
       </c>
-      <c r="H123" s="9">
+      <c r="H123" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11390,16 +11402,16 @@
       <c r="D124" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E124" s="9">
+      <c r="E124" s="8">
         <v>9128</v>
       </c>
-      <c r="F124" s="9">
+      <c r="F124" s="8">
         <v>2070555</v>
       </c>
-      <c r="G124" s="9">
+      <c r="G124" s="8">
         <v>73</v>
       </c>
-      <c r="H124" s="9">
+      <c r="H124" s="8">
         <v>109</v>
       </c>
     </row>
@@ -11416,16 +11428,16 @@
       <c r="D125" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E125" s="9">
+      <c r="E125" s="8">
         <v>106</v>
       </c>
-      <c r="F125" s="9">
+      <c r="F125" s="8">
         <v>6</v>
       </c>
-      <c r="G125" s="9">
+      <c r="G125" s="8">
         <v>0</v>
       </c>
-      <c r="H125" s="9">
+      <c r="H125" s="8">
         <v>2</v>
       </c>
     </row>
@@ -11442,16 +11454,16 @@
       <c r="D126" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E126" s="9">
+      <c r="E126" s="8">
         <v>24</v>
       </c>
-      <c r="F126" s="9">
+      <c r="F126" s="8">
         <v>708</v>
       </c>
-      <c r="G126" s="9">
+      <c r="G126" s="8">
         <v>0</v>
       </c>
-      <c r="H126" s="9">
+      <c r="H126" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11468,16 +11480,16 @@
       <c r="D127" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E127" s="9">
+      <c r="E127" s="8">
         <v>20</v>
       </c>
-      <c r="F127" s="9">
+      <c r="F127" s="8">
         <v>19194</v>
       </c>
-      <c r="G127" s="9">
+      <c r="G127" s="8">
         <v>0</v>
       </c>
-      <c r="H127" s="9">
+      <c r="H127" s="8">
         <v>9</v>
       </c>
     </row>
@@ -11494,16 +11506,16 @@
       <c r="D128" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E128" s="9">
+      <c r="E128" s="8">
         <v>5</v>
       </c>
-      <c r="F128" s="9">
+      <c r="F128" s="8">
         <v>495</v>
       </c>
-      <c r="G128" s="9">
+      <c r="G128" s="8">
         <v>0</v>
       </c>
-      <c r="H128" s="9">
+      <c r="H128" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11520,16 +11532,16 @@
       <c r="D129" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E129" s="9">
+      <c r="E129" s="8">
         <v>4</v>
       </c>
-      <c r="F129" s="9">
+      <c r="F129" s="8">
         <v>1</v>
       </c>
-      <c r="G129" s="9">
+      <c r="G129" s="8">
         <v>0</v>
       </c>
-      <c r="H129" s="9">
+      <c r="H129" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11546,16 +11558,16 @@
       <c r="D130" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E130" s="9">
+      <c r="E130" s="8">
         <v>2</v>
       </c>
-      <c r="F130" s="9">
+      <c r="F130" s="8">
         <v>24</v>
       </c>
-      <c r="G130" s="9">
+      <c r="G130" s="8">
         <v>0</v>
       </c>
-      <c r="H130" s="9">
+      <c r="H130" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11572,16 +11584,16 @@
       <c r="D131" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E131" s="9">
+      <c r="E131" s="8">
         <v>5</v>
       </c>
-      <c r="F131" s="9">
+      <c r="F131" s="8">
         <v>638</v>
       </c>
-      <c r="G131" s="9">
+      <c r="G131" s="8">
         <v>0</v>
       </c>
-      <c r="H131" s="9">
+      <c r="H131" s="8">
         <v>1</v>
       </c>
     </row>
@@ -11598,16 +11610,16 @@
       <c r="D132" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E132" s="9">
+      <c r="E132" s="8">
         <v>1</v>
       </c>
-      <c r="F132" s="9">
+      <c r="F132" s="8">
         <v>2</v>
       </c>
-      <c r="G132" s="9">
+      <c r="G132" s="8">
         <v>0</v>
       </c>
-      <c r="H132" s="9">
+      <c r="H132" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11624,16 +11636,16 @@
       <c r="D133" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="8">
         <v>294</v>
       </c>
-      <c r="F133" s="9">
+      <c r="F133" s="8">
         <v>99930</v>
       </c>
-      <c r="G133" s="9">
+      <c r="G133" s="8">
         <v>0</v>
       </c>
-      <c r="H133" s="9">
+      <c r="H133" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11650,16 +11662,16 @@
       <c r="D134" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E134" s="9">
+      <c r="E134" s="8">
         <v>44</v>
       </c>
-      <c r="F134" s="9">
+      <c r="F134" s="8">
         <v>980</v>
       </c>
-      <c r="G134" s="9">
+      <c r="G134" s="8">
         <v>0</v>
       </c>
-      <c r="H134" s="9">
+      <c r="H134" s="8">
         <v>7</v>
       </c>
     </row>
@@ -11676,16 +11688,16 @@
       <c r="D135" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E135" s="9">
+      <c r="E135" s="8">
         <v>2</v>
       </c>
-      <c r="F135" s="9">
+      <c r="F135" s="8">
         <v>19</v>
       </c>
-      <c r="G135" s="9">
+      <c r="G135" s="8">
         <v>0</v>
       </c>
-      <c r="H135" s="9">
+      <c r="H135" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11702,16 +11714,16 @@
       <c r="D136" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E136" s="9">
+      <c r="E136" s="8">
         <v>6422</v>
       </c>
-      <c r="F136" s="9">
+      <c r="F136" s="8">
         <v>763999</v>
       </c>
-      <c r="G136" s="9">
+      <c r="G136" s="8">
         <v>671</v>
       </c>
-      <c r="H136" s="9">
+      <c r="H136" s="8">
         <v>801</v>
       </c>
     </row>
@@ -11728,16 +11740,16 @@
       <c r="D137" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E137" s="9">
+      <c r="E137" s="8">
         <v>120</v>
       </c>
-      <c r="F137" s="9">
+      <c r="F137" s="8">
         <v>22373</v>
       </c>
-      <c r="G137" s="9">
+      <c r="G137" s="8">
         <v>0</v>
       </c>
-      <c r="H137" s="9">
+      <c r="H137" s="8">
         <v>25</v>
       </c>
     </row>
@@ -11754,16 +11766,16 @@
       <c r="D138" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E138" s="9">
+      <c r="E138" s="8">
         <v>6026</v>
       </c>
-      <c r="F138" s="9">
+      <c r="F138" s="8">
         <v>4116251</v>
       </c>
-      <c r="G138" s="9">
+      <c r="G138" s="8">
         <v>133</v>
       </c>
-      <c r="H138" s="9">
+      <c r="H138" s="8">
         <v>193</v>
       </c>
     </row>
@@ -11780,16 +11792,16 @@
       <c r="D139" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E139" s="9">
+      <c r="E139" s="8">
         <v>14</v>
       </c>
-      <c r="F139" s="9">
+      <c r="F139" s="8">
         <v>6195</v>
       </c>
-      <c r="G139" s="9">
+      <c r="G139" s="8">
         <v>0</v>
       </c>
-      <c r="H139" s="9">
+      <c r="H139" s="8">
         <v>1</v>
       </c>
     </row>
@@ -11806,16 +11818,16 @@
       <c r="D140" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E140" s="9">
+      <c r="E140" s="8">
         <v>25</v>
       </c>
-      <c r="F140" s="9">
+      <c r="F140" s="8">
         <v>30711</v>
       </c>
-      <c r="G140" s="9">
+      <c r="G140" s="8">
         <v>2</v>
       </c>
-      <c r="H140" s="9">
+      <c r="H140" s="8">
         <v>7</v>
       </c>
     </row>
@@ -11832,16 +11844,16 @@
       <c r="D141" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E141" s="9">
+      <c r="E141" s="8">
         <v>10</v>
       </c>
-      <c r="F141" s="9">
+      <c r="F141" s="8">
         <v>75532</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G141" s="8">
         <v>0</v>
       </c>
-      <c r="H141" s="9">
+      <c r="H141" s="8">
         <v>4</v>
       </c>
     </row>
@@ -11858,16 +11870,16 @@
       <c r="D142" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E142" s="9">
+      <c r="E142" s="8">
         <v>4</v>
       </c>
-      <c r="F142" s="9">
+      <c r="F142" s="8">
         <v>987</v>
       </c>
-      <c r="G142" s="9">
+      <c r="G142" s="8">
         <v>0</v>
       </c>
-      <c r="H142" s="9">
+      <c r="H142" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11884,16 +11896,16 @@
       <c r="D143" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E143" s="9">
+      <c r="E143" s="8">
         <v>606</v>
       </c>
-      <c r="F143" s="9">
+      <c r="F143" s="8">
         <v>240426</v>
       </c>
-      <c r="G143" s="9">
+      <c r="G143" s="8">
         <v>135</v>
       </c>
-      <c r="H143" s="9">
+      <c r="H143" s="8">
         <v>136</v>
       </c>
     </row>
@@ -11910,16 +11922,16 @@
       <c r="D144" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E144" s="9">
+      <c r="E144" s="8">
         <v>250</v>
       </c>
-      <c r="F144" s="9">
+      <c r="F144" s="8">
         <v>19294</v>
       </c>
-      <c r="G144" s="9">
+      <c r="G144" s="8">
         <v>0</v>
       </c>
-      <c r="H144" s="9">
+      <c r="H144" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11936,16 +11948,16 @@
       <c r="D145" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="9">
+      <c r="E145" s="8">
         <v>242</v>
       </c>
-      <c r="F145" s="9">
+      <c r="F145" s="8">
         <v>97597</v>
       </c>
-      <c r="G145" s="9">
+      <c r="G145" s="8">
         <v>14</v>
       </c>
-      <c r="H145" s="9">
+      <c r="H145" s="8">
         <v>14</v>
       </c>
     </row>
@@ -11962,16 +11974,16 @@
       <c r="D146" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E146" s="9">
+      <c r="E146" s="8">
         <v>5</v>
       </c>
-      <c r="F146" s="9">
+      <c r="F146" s="8">
         <v>985</v>
       </c>
-      <c r="G146" s="9">
+      <c r="G146" s="8">
         <v>0</v>
       </c>
-      <c r="H146" s="9">
+      <c r="H146" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11988,16 +12000,16 @@
       <c r="D147" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E147" s="9">
+      <c r="E147" s="8">
         <v>2581</v>
       </c>
-      <c r="F147" s="9">
+      <c r="F147" s="8">
         <v>1296517</v>
       </c>
-      <c r="G147" s="9">
+      <c r="G147" s="8">
         <v>94</v>
       </c>
-      <c r="H147" s="9">
+      <c r="H147" s="8">
         <v>388</v>
       </c>
     </row>
@@ -12014,16 +12026,16 @@
       <c r="D148" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E148" s="9">
+      <c r="E148" s="8">
         <v>18</v>
       </c>
-      <c r="F148" s="9">
+      <c r="F148" s="8">
         <v>1145</v>
       </c>
-      <c r="G148" s="9">
+      <c r="G148" s="8">
         <v>0</v>
       </c>
-      <c r="H148" s="9">
+      <c r="H148" s="8">
         <v>4</v>
       </c>
     </row>
@@ -12040,16 +12052,16 @@
       <c r="D149" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E149" s="9">
+      <c r="E149" s="8">
         <v>746</v>
       </c>
-      <c r="F149" s="9">
+      <c r="F149" s="8">
         <v>1881631</v>
       </c>
-      <c r="G149" s="9">
+      <c r="G149" s="8">
         <v>30</v>
       </c>
-      <c r="H149" s="9">
+      <c r="H149" s="8">
         <v>57</v>
       </c>
     </row>
@@ -12066,16 +12078,16 @@
       <c r="D150" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E150" s="9">
+      <c r="E150" s="8">
         <v>24</v>
       </c>
-      <c r="F150" s="9">
+      <c r="F150" s="8">
         <v>18432</v>
       </c>
-      <c r="G150" s="9">
+      <c r="G150" s="8">
         <v>0</v>
       </c>
-      <c r="H150" s="9">
+      <c r="H150" s="8">
         <v>3</v>
       </c>
     </row>
@@ -12092,16 +12104,16 @@
       <c r="D151" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="9">
+      <c r="E151" s="8">
         <v>1846</v>
       </c>
-      <c r="F151" s="9">
+      <c r="F151" s="8">
         <v>1864840</v>
       </c>
-      <c r="G151" s="9">
+      <c r="G151" s="8">
         <v>90</v>
       </c>
-      <c r="H151" s="9">
+      <c r="H151" s="8">
         <v>93</v>
       </c>
     </row>
@@ -12118,16 +12130,16 @@
       <c r="D152" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E152" s="9">
+      <c r="E152" s="8">
         <v>273</v>
       </c>
-      <c r="F152" s="9">
+      <c r="F152" s="8">
         <v>292237</v>
       </c>
-      <c r="G152" s="9">
+      <c r="G152" s="8">
         <v>0</v>
       </c>
-      <c r="H152" s="9">
+      <c r="H152" s="8">
         <v>8</v>
       </c>
     </row>
@@ -12144,16 +12156,16 @@
       <c r="D153" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E153" s="9">
+      <c r="E153" s="8">
         <v>100</v>
       </c>
-      <c r="F153" s="9">
+      <c r="F153" s="8">
         <v>158476</v>
       </c>
-      <c r="G153" s="9">
+      <c r="G153" s="8">
         <v>9</v>
       </c>
-      <c r="H153" s="9">
+      <c r="H153" s="8">
         <v>9</v>
       </c>
     </row>
@@ -12170,16 +12182,16 @@
       <c r="D154" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E154" s="9">
+      <c r="E154" s="8">
         <v>6</v>
       </c>
-      <c r="F154" s="9">
+      <c r="F154" s="8">
         <v>175</v>
       </c>
-      <c r="G154" s="9">
+      <c r="G154" s="8">
         <v>0</v>
       </c>
-      <c r="H154" s="9">
+      <c r="H154" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12196,16 +12208,16 @@
       <c r="D155" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E155" s="9">
+      <c r="E155" s="8">
         <v>14</v>
       </c>
-      <c r="F155" s="9">
+      <c r="F155" s="8">
         <v>31</v>
       </c>
-      <c r="G155" s="9">
+      <c r="G155" s="8">
         <v>0</v>
       </c>
-      <c r="H155" s="9">
+      <c r="H155" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12222,16 +12234,16 @@
       <c r="D156" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E156" s="9">
+      <c r="E156" s="8">
         <v>14</v>
       </c>
-      <c r="F156" s="9">
+      <c r="F156" s="8">
         <v>1</v>
       </c>
-      <c r="G156" s="9">
+      <c r="G156" s="8">
         <v>0</v>
       </c>
-      <c r="H156" s="9">
+      <c r="H156" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12248,16 +12260,16 @@
       <c r="D157" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E157" s="9">
+      <c r="E157" s="8">
         <v>17</v>
       </c>
-      <c r="F157" s="9">
+      <c r="F157" s="8">
         <v>585012</v>
       </c>
-      <c r="G157" s="9">
+      <c r="G157" s="8">
         <v>0</v>
       </c>
-      <c r="H157" s="9">
+      <c r="H157" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12274,16 +12286,16 @@
       <c r="D158" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E158" s="9">
+      <c r="E158" s="8">
         <v>38</v>
       </c>
-      <c r="F158" s="9">
+      <c r="F158" s="8">
         <v>1899</v>
       </c>
-      <c r="G158" s="9">
+      <c r="G158" s="8">
         <v>0</v>
       </c>
-      <c r="H158" s="9">
+      <c r="H158" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12300,16 +12312,16 @@
       <c r="D159" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E159" s="9">
+      <c r="E159" s="8">
         <v>8</v>
       </c>
-      <c r="F159" s="9">
+      <c r="F159" s="8">
         <v>33</v>
       </c>
-      <c r="G159" s="9">
+      <c r="G159" s="8">
         <v>0</v>
       </c>
-      <c r="H159" s="9">
+      <c r="H159" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12326,16 +12338,16 @@
       <c r="D160" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E160" s="9">
+      <c r="E160" s="8">
         <v>206</v>
       </c>
-      <c r="F160" s="9">
+      <c r="F160" s="8">
         <v>281332</v>
       </c>
-      <c r="G160" s="9">
+      <c r="G160" s="8">
         <v>15</v>
       </c>
-      <c r="H160" s="9">
+      <c r="H160" s="8">
         <v>64</v>
       </c>
     </row>
@@ -12352,16 +12364,16 @@
       <c r="D161" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E161" s="9">
+      <c r="E161" s="8">
         <v>30</v>
       </c>
-      <c r="F161" s="9">
+      <c r="F161" s="8">
         <v>257</v>
       </c>
-      <c r="G161" s="9">
+      <c r="G161" s="8">
         <v>0</v>
       </c>
-      <c r="H161" s="9">
+      <c r="H161" s="8">
         <v>4</v>
       </c>
     </row>
@@ -12378,16 +12390,16 @@
       <c r="D162" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E162" s="9">
+      <c r="E162" s="8">
         <v>4</v>
       </c>
-      <c r="F162" s="9">
+      <c r="F162" s="8">
         <v>3</v>
       </c>
-      <c r="G162" s="9">
+      <c r="G162" s="8">
         <v>0</v>
       </c>
-      <c r="H162" s="9">
+      <c r="H162" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12404,16 +12416,16 @@
       <c r="D163" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E163" s="9">
+      <c r="E163" s="8">
         <v>5</v>
       </c>
-      <c r="F163" s="9">
+      <c r="F163" s="8">
         <v>1417</v>
       </c>
-      <c r="G163" s="9">
+      <c r="G163" s="8">
         <v>0</v>
       </c>
-      <c r="H163" s="9">
+      <c r="H163" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12430,16 +12442,16 @@
       <c r="D164" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E164" s="9">
+      <c r="E164" s="8">
         <v>5</v>
       </c>
-      <c r="F164" s="9">
+      <c r="F164" s="8">
         <v>3020</v>
       </c>
-      <c r="G164" s="9">
+      <c r="G164" s="8">
         <v>0</v>
       </c>
-      <c r="H164" s="9">
+      <c r="H164" s="8">
         <v>3</v>
       </c>
     </row>
@@ -12456,16 +12468,16 @@
       <c r="D165" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E165" s="9">
+      <c r="E165" s="8">
         <v>2</v>
       </c>
-      <c r="F165" s="9">
+      <c r="F165" s="8">
         <v>21</v>
       </c>
-      <c r="G165" s="9">
+      <c r="G165" s="8">
         <v>0</v>
       </c>
-      <c r="H165" s="9">
+      <c r="H165" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12482,16 +12494,16 @@
       <c r="D166" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E166" s="9">
+      <c r="E166" s="8">
         <v>2651</v>
       </c>
-      <c r="F166" s="9">
+      <c r="F166" s="8">
         <v>1137819</v>
       </c>
-      <c r="G166" s="9">
+      <c r="G166" s="8">
         <v>327</v>
       </c>
-      <c r="H166" s="9">
+      <c r="H166" s="8">
         <v>516</v>
       </c>
     </row>
@@ -12508,16 +12520,16 @@
       <c r="D167" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E167" s="9">
+      <c r="E167" s="8">
         <v>142</v>
       </c>
-      <c r="F167" s="9">
+      <c r="F167" s="8">
         <v>14329</v>
       </c>
-      <c r="G167" s="9">
+      <c r="G167" s="8">
         <v>0</v>
       </c>
-      <c r="H167" s="9">
+      <c r="H167" s="8">
         <v>26</v>
       </c>
     </row>
@@ -12534,16 +12546,16 @@
       <c r="D168" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E168" s="9">
+      <c r="E168" s="8">
         <v>10630</v>
       </c>
-      <c r="F168" s="9">
+      <c r="F168" s="8">
         <v>1425256</v>
       </c>
-      <c r="G168" s="9">
+      <c r="G168" s="8">
         <v>253</v>
       </c>
-      <c r="H168" s="9">
+      <c r="H168" s="8">
         <v>482</v>
       </c>
     </row>
@@ -12560,16 +12572,16 @@
       <c r="D169" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E169" s="9">
+      <c r="E169" s="8">
         <v>82</v>
       </c>
-      <c r="F169" s="9">
+      <c r="F169" s="8">
         <v>4635</v>
       </c>
-      <c r="G169" s="9">
+      <c r="G169" s="8">
         <v>0</v>
       </c>
-      <c r="H169" s="9">
+      <c r="H169" s="8">
         <v>13</v>
       </c>
     </row>
@@ -12586,16 +12598,16 @@
       <c r="D170" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E170" s="9">
+      <c r="E170" s="8">
         <v>73</v>
       </c>
-      <c r="F170" s="9">
+      <c r="F170" s="8">
         <v>54511</v>
       </c>
-      <c r="G170" s="9">
+      <c r="G170" s="8">
         <v>12</v>
       </c>
-      <c r="H170" s="9">
+      <c r="H170" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12612,16 +12624,16 @@
       <c r="D171" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E171" s="9">
+      <c r="E171" s="8">
         <v>4</v>
       </c>
-      <c r="F171" s="9">
+      <c r="F171" s="8">
         <v>59</v>
       </c>
-      <c r="G171" s="9">
+      <c r="G171" s="8">
         <v>0</v>
       </c>
-      <c r="H171" s="9">
+      <c r="H171" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12638,16 +12650,16 @@
       <c r="D172" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E172" s="9">
+      <c r="E172" s="8">
         <v>1</v>
       </c>
-      <c r="F172" s="9">
+      <c r="F172" s="8">
         <v>31</v>
       </c>
-      <c r="G172" s="9">
+      <c r="G172" s="8">
         <v>0</v>
       </c>
-      <c r="H172" s="9">
+      <c r="H172" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12664,16 +12676,16 @@
       <c r="D173" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E173" s="9">
+      <c r="E173" s="8">
         <v>6</v>
       </c>
-      <c r="F173" s="9">
+      <c r="F173" s="8">
         <v>18199</v>
       </c>
-      <c r="G173" s="9">
+      <c r="G173" s="8">
         <v>0</v>
       </c>
-      <c r="H173" s="9">
+      <c r="H173" s="8">
         <v>3</v>
       </c>
     </row>
@@ -12690,16 +12702,16 @@
       <c r="D174" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E174" s="9">
+      <c r="E174" s="8">
         <v>14</v>
       </c>
-      <c r="F174" s="9">
+      <c r="F174" s="8">
         <v>4991</v>
       </c>
-      <c r="G174" s="9">
+      <c r="G174" s="8">
         <v>0</v>
       </c>
-      <c r="H174" s="9">
+      <c r="H174" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12716,16 +12728,16 @@
       <c r="D175" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E175" s="9">
+      <c r="E175" s="8">
         <v>35</v>
       </c>
-      <c r="F175" s="9">
+      <c r="F175" s="8">
         <v>3982</v>
       </c>
-      <c r="G175" s="9">
+      <c r="G175" s="8">
         <v>0</v>
       </c>
-      <c r="H175" s="9">
+      <c r="H175" s="8">
         <v>3</v>
       </c>
     </row>
@@ -12742,16 +12754,16 @@
       <c r="D176" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E176" s="9">
+      <c r="E176" s="8">
         <v>90</v>
       </c>
-      <c r="F176" s="9">
+      <c r="F176" s="8">
         <v>594913</v>
       </c>
-      <c r="G176" s="9">
+      <c r="G176" s="8">
         <v>0</v>
       </c>
-      <c r="H176" s="9">
+      <c r="H176" s="8">
         <v>38</v>
       </c>
     </row>
@@ -12768,16 +12780,16 @@
       <c r="D177" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E177" s="9">
+      <c r="E177" s="8">
         <v>12</v>
       </c>
-      <c r="F177" s="9">
+      <c r="F177" s="8">
         <v>382733</v>
       </c>
-      <c r="G177" s="9">
+      <c r="G177" s="8">
         <v>0</v>
       </c>
-      <c r="H177" s="9">
+      <c r="H177" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12794,16 +12806,16 @@
       <c r="D178" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E178" s="9">
+      <c r="E178" s="8">
         <v>183</v>
       </c>
-      <c r="F178" s="9">
+      <c r="F178" s="8">
         <v>354818</v>
       </c>
-      <c r="G178" s="9">
+      <c r="G178" s="8">
         <v>0</v>
       </c>
-      <c r="H178" s="9">
+      <c r="H178" s="8">
         <v>62</v>
       </c>
     </row>
@@ -12820,16 +12832,16 @@
       <c r="D179" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E179" s="9">
+      <c r="E179" s="8">
         <v>6</v>
       </c>
-      <c r="F179" s="9">
+      <c r="F179" s="8">
         <v>83953</v>
       </c>
-      <c r="G179" s="9">
+      <c r="G179" s="8">
         <v>0</v>
       </c>
-      <c r="H179" s="9">
+      <c r="H179" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12846,16 +12858,16 @@
       <c r="D180" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E180" s="9">
+      <c r="E180" s="8">
         <v>712</v>
       </c>
-      <c r="F180" s="9">
+      <c r="F180" s="8">
         <v>68543</v>
       </c>
-      <c r="G180" s="9">
+      <c r="G180" s="8">
         <v>14</v>
       </c>
-      <c r="H180" s="9">
+      <c r="H180" s="8">
         <v>20</v>
       </c>
     </row>
@@ -12872,16 +12884,16 @@
       <c r="D181" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E181" s="9">
+      <c r="E181" s="8">
         <v>257</v>
       </c>
-      <c r="F181" s="9">
+      <c r="F181" s="8">
         <v>12265</v>
       </c>
-      <c r="G181" s="9">
+      <c r="G181" s="8">
         <v>0</v>
       </c>
-      <c r="H181" s="9">
+      <c r="H181" s="8">
         <v>12</v>
       </c>
     </row>
@@ -12898,16 +12910,16 @@
       <c r="D182" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E182" s="9">
+      <c r="E182" s="8">
         <v>21</v>
       </c>
-      <c r="F182" s="9">
+      <c r="F182" s="8">
         <v>36455</v>
       </c>
-      <c r="G182" s="9">
+      <c r="G182" s="8">
         <v>0</v>
       </c>
-      <c r="H182" s="9">
+      <c r="H182" s="8">
         <v>0</v>
       </c>
     </row>
@@ -12924,16 +12936,16 @@
       <c r="D183" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E183" s="9">
+      <c r="E183" s="8">
         <v>4</v>
       </c>
-      <c r="F183" s="9">
+      <c r="F183" s="8">
         <v>4569</v>
       </c>
-      <c r="G183" s="9">
+      <c r="G183" s="8">
         <v>0</v>
       </c>
-      <c r="H183" s="9">
+      <c r="H183" s="8">
         <v>2</v>
       </c>
     </row>
@@ -12950,16 +12962,16 @@
       <c r="D184" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E184" s="9">
+      <c r="E184" s="8">
         <v>2</v>
       </c>
-      <c r="F184" s="9">
+      <c r="F184" s="8">
         <v>896</v>
       </c>
-      <c r="G184" s="9">
+      <c r="G184" s="8">
         <v>0</v>
       </c>
-      <c r="H184" s="9">
+      <c r="H184" s="8">
         <v>1</v>
       </c>
     </row>
@@ -12976,16 +12988,16 @@
       <c r="D185" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E185" s="9">
+      <c r="E185" s="8">
         <v>22</v>
       </c>
-      <c r="F185" s="9">
+      <c r="F185" s="8">
         <v>907</v>
       </c>
-      <c r="G185" s="9">
+      <c r="G185" s="8">
         <v>0</v>
       </c>
-      <c r="H185" s="9">
+      <c r="H185" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13002,16 +13014,16 @@
       <c r="D186" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E186" s="9">
+      <c r="E186" s="8">
         <v>4</v>
       </c>
-      <c r="F186" s="9">
+      <c r="F186" s="8">
         <v>213055</v>
       </c>
-      <c r="G186" s="9">
+      <c r="G186" s="8">
         <v>0</v>
       </c>
-      <c r="H186" s="9">
+      <c r="H186" s="8">
         <v>1</v>
       </c>
     </row>
@@ -13028,16 +13040,16 @@
       <c r="D187" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E187" s="9">
+      <c r="E187" s="8">
         <v>2</v>
       </c>
-      <c r="F187" s="9">
+      <c r="F187" s="8">
         <v>2</v>
       </c>
-      <c r="G187" s="9">
+      <c r="G187" s="8">
         <v>0</v>
       </c>
-      <c r="H187" s="9">
+      <c r="H187" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13054,16 +13066,16 @@
       <c r="D188" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E188" s="9">
+      <c r="E188" s="8">
         <v>1</v>
       </c>
-      <c r="F188" s="9">
+      <c r="F188" s="8">
         <v>37</v>
       </c>
-      <c r="G188" s="9">
+      <c r="G188" s="8">
         <v>0</v>
       </c>
-      <c r="H188" s="9">
+      <c r="H188" s="8">
         <v>1</v>
       </c>
     </row>
@@ -13080,16 +13092,16 @@
       <c r="D189" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E189" s="9">
+      <c r="E189" s="8">
         <v>26</v>
       </c>
-      <c r="F189" s="9">
+      <c r="F189" s="8">
         <v>9091</v>
       </c>
-      <c r="G189" s="9">
+      <c r="G189" s="8">
         <v>0</v>
       </c>
-      <c r="H189" s="9">
+      <c r="H189" s="8">
         <v>1</v>
       </c>
     </row>
@@ -13106,16 +13118,16 @@
       <c r="D190" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E190" s="9">
+      <c r="E190" s="8">
         <v>4</v>
       </c>
-      <c r="F190" s="9">
+      <c r="F190" s="8">
         <v>9737</v>
       </c>
-      <c r="G190" s="9">
+      <c r="G190" s="8">
         <v>0</v>
       </c>
-      <c r="H190" s="9">
+      <c r="H190" s="8">
         <v>1</v>
       </c>
     </row>
@@ -13132,16 +13144,16 @@
       <c r="D191" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E191" s="9">
+      <c r="E191" s="8">
         <v>10</v>
       </c>
-      <c r="F191" s="9">
+      <c r="F191" s="8">
         <v>1369</v>
       </c>
-      <c r="G191" s="9">
+      <c r="G191" s="8">
         <v>0</v>
       </c>
-      <c r="H191" s="9">
+      <c r="H191" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13158,16 +13170,16 @@
       <c r="D192" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E192" s="9">
+      <c r="E192" s="8">
         <v>1717</v>
       </c>
-      <c r="F192" s="9">
+      <c r="F192" s="8">
         <v>616676</v>
       </c>
-      <c r="G192" s="9">
+      <c r="G192" s="8">
         <v>112</v>
       </c>
-      <c r="H192" s="9">
+      <c r="H192" s="8">
         <v>354</v>
       </c>
     </row>
@@ -13184,16 +13196,16 @@
       <c r="D193" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E193" s="9">
+      <c r="E193" s="8">
         <v>32</v>
       </c>
-      <c r="F193" s="9">
+      <c r="F193" s="8">
         <v>13982</v>
       </c>
-      <c r="G193" s="9">
+      <c r="G193" s="8">
         <v>0</v>
       </c>
-      <c r="H193" s="9">
+      <c r="H193" s="8">
         <v>7</v>
       </c>
     </row>
@@ -13210,16 +13222,16 @@
       <c r="D194" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E194" s="9">
+      <c r="E194" s="8">
         <v>1092</v>
       </c>
-      <c r="F194" s="9">
+      <c r="F194" s="8">
         <v>580758</v>
       </c>
-      <c r="G194" s="9">
+      <c r="G194" s="8">
         <v>71</v>
       </c>
-      <c r="H194" s="9">
+      <c r="H194" s="8">
         <v>167</v>
       </c>
     </row>
@@ -13236,16 +13248,16 @@
       <c r="D195" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E195" s="9">
+      <c r="E195" s="8">
         <v>213</v>
       </c>
-      <c r="F195" s="9">
+      <c r="F195" s="8">
         <v>103815</v>
       </c>
-      <c r="G195" s="9">
+      <c r="G195" s="8">
         <v>0</v>
       </c>
-      <c r="H195" s="9">
+      <c r="H195" s="8">
         <v>85</v>
       </c>
     </row>
@@ -13262,16 +13274,16 @@
       <c r="D196" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E196" s="9">
+      <c r="E196" s="8">
         <v>1179</v>
       </c>
-      <c r="F196" s="9">
+      <c r="F196" s="8">
         <v>1071044</v>
       </c>
-      <c r="G196" s="9">
+      <c r="G196" s="8">
         <v>67</v>
       </c>
-      <c r="H196" s="9">
+      <c r="H196" s="8">
         <v>123</v>
       </c>
     </row>
@@ -13288,16 +13300,16 @@
       <c r="D197" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E197" s="9">
+      <c r="E197" s="8">
         <v>53</v>
       </c>
-      <c r="F197" s="9">
+      <c r="F197" s="8">
         <v>705370</v>
       </c>
-      <c r="G197" s="9">
+      <c r="G197" s="8">
         <v>0</v>
       </c>
-      <c r="H197" s="9">
+      <c r="H197" s="8">
         <v>14</v>
       </c>
     </row>
@@ -13314,16 +13326,16 @@
       <c r="D198" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E198" s="9">
+      <c r="E198" s="8">
         <v>1085</v>
       </c>
-      <c r="F198" s="9">
+      <c r="F198" s="8">
         <v>5144930</v>
       </c>
-      <c r="G198" s="9">
+      <c r="G198" s="8">
         <v>18</v>
       </c>
-      <c r="H198" s="9">
+      <c r="H198" s="8">
         <v>429</v>
       </c>
     </row>
@@ -13340,16 +13352,16 @@
       <c r="D199" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E199" s="9">
+      <c r="E199" s="8">
         <v>19</v>
       </c>
-      <c r="F199" s="9">
+      <c r="F199" s="8">
         <v>8589</v>
       </c>
-      <c r="G199" s="9">
+      <c r="G199" s="8">
         <v>0</v>
       </c>
-      <c r="H199" s="9">
+      <c r="H199" s="8">
         <v>1</v>
       </c>
     </row>
@@ -13366,16 +13378,16 @@
       <c r="D200" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E200" s="9">
+      <c r="E200" s="8">
         <v>1</v>
       </c>
-      <c r="F200" s="9">
+      <c r="F200" s="8">
         <v>0</v>
       </c>
-      <c r="G200" s="9">
+      <c r="G200" s="8">
         <v>0</v>
       </c>
-      <c r="H200" s="9">
+      <c r="H200" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13392,16 +13404,16 @@
       <c r="D201" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E201" s="9">
+      <c r="E201" s="8">
         <v>115</v>
       </c>
-      <c r="F201" s="9">
+      <c r="F201" s="8">
         <v>1133587</v>
       </c>
-      <c r="G201" s="9">
+      <c r="G201" s="8">
         <v>0</v>
       </c>
-      <c r="H201" s="9">
+      <c r="H201" s="8">
         <v>66</v>
       </c>
     </row>
@@ -13418,16 +13430,16 @@
       <c r="D202" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E202" s="9">
+      <c r="E202" s="8">
         <v>12</v>
       </c>
-      <c r="F202" s="9">
+      <c r="F202" s="8">
         <v>290</v>
       </c>
-      <c r="G202" s="9">
+      <c r="G202" s="8">
         <v>0</v>
       </c>
-      <c r="H202" s="9">
+      <c r="H202" s="8">
         <v>3</v>
       </c>
     </row>
@@ -13444,16 +13456,16 @@
       <c r="D203" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E203" s="9">
+      <c r="E203" s="8">
         <v>599</v>
       </c>
-      <c r="F203" s="9">
+      <c r="F203" s="8">
         <v>1655001</v>
       </c>
-      <c r="G203" s="9">
+      <c r="G203" s="8">
         <v>26</v>
       </c>
-      <c r="H203" s="9">
+      <c r="H203" s="8">
         <v>153</v>
       </c>
     </row>
@@ -13470,16 +13482,16 @@
       <c r="D204" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E204" s="9">
+      <c r="E204" s="8">
         <v>126</v>
       </c>
-      <c r="F204" s="9">
+      <c r="F204" s="8">
         <v>7751</v>
       </c>
-      <c r="G204" s="9">
+      <c r="G204" s="8">
         <v>0</v>
       </c>
-      <c r="H204" s="9">
+      <c r="H204" s="8">
         <v>14</v>
       </c>
     </row>
@@ -13496,16 +13508,16 @@
       <c r="D205" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E205" s="9">
-        <v>79</v>
-      </c>
-      <c r="F205" s="9">
+      <c r="E205" s="8">
+        <v>79</v>
+      </c>
+      <c r="F205" s="8">
         <v>684886</v>
       </c>
-      <c r="G205" s="9">
+      <c r="G205" s="8">
         <v>1</v>
       </c>
-      <c r="H205" s="9">
+      <c r="H205" s="8">
         <v>57</v>
       </c>
     </row>
@@ -13522,16 +13534,16 @@
       <c r="D206" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E206" s="9">
+      <c r="E206" s="8">
         <v>20</v>
       </c>
-      <c r="F206" s="9">
+      <c r="F206" s="8">
         <v>7117</v>
       </c>
-      <c r="G206" s="9">
+      <c r="G206" s="8">
         <v>0</v>
       </c>
-      <c r="H206" s="9">
+      <c r="H206" s="8">
         <v>3</v>
       </c>
     </row>
@@ -13548,16 +13560,16 @@
       <c r="D207" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E207" s="9">
+      <c r="E207" s="8">
         <v>80</v>
       </c>
-      <c r="F207" s="9">
+      <c r="F207" s="8">
         <v>29279</v>
       </c>
-      <c r="G207" s="9">
+      <c r="G207" s="8">
         <v>39</v>
       </c>
-      <c r="H207" s="9">
+      <c r="H207" s="8">
         <v>39</v>
       </c>
     </row>
@@ -13574,16 +13586,16 @@
       <c r="D208" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E208" s="9">
+      <c r="E208" s="8">
         <v>26</v>
       </c>
-      <c r="F208" s="9">
+      <c r="F208" s="8">
         <v>113291</v>
       </c>
-      <c r="G208" s="9">
+      <c r="G208" s="8">
         <v>0</v>
       </c>
-      <c r="H208" s="9">
+      <c r="H208" s="8">
         <v>4</v>
       </c>
     </row>
@@ -13600,16 +13612,16 @@
       <c r="D209" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E209" s="9">
+      <c r="E209" s="8">
         <v>3612</v>
       </c>
-      <c r="F209" s="9">
+      <c r="F209" s="8">
         <v>3819680</v>
       </c>
-      <c r="G209" s="9">
+      <c r="G209" s="8">
         <v>155</v>
       </c>
-      <c r="H209" s="9">
+      <c r="H209" s="8">
         <v>163</v>
       </c>
     </row>
@@ -13626,16 +13638,16 @@
       <c r="D210" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E210" s="9">
+      <c r="E210" s="8">
         <v>42</v>
       </c>
-      <c r="F210" s="9">
+      <c r="F210" s="8">
         <v>11312</v>
       </c>
-      <c r="G210" s="9">
+      <c r="G210" s="8">
         <v>0</v>
       </c>
-      <c r="H210" s="9">
+      <c r="H210" s="8">
         <v>1</v>
       </c>
     </row>
@@ -13652,16 +13664,16 @@
       <c r="D211" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E211" s="9">
+      <c r="E211" s="8">
         <v>10144</v>
       </c>
-      <c r="F211" s="9">
+      <c r="F211" s="8">
         <v>49088493</v>
       </c>
-      <c r="G211" s="9">
+      <c r="G211" s="8">
         <v>342</v>
       </c>
-      <c r="H211" s="9">
+      <c r="H211" s="8">
         <v>503</v>
       </c>
     </row>
@@ -13678,16 +13690,16 @@
       <c r="D212" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E212" s="9">
+      <c r="E212" s="8">
         <v>180</v>
       </c>
-      <c r="F212" s="9">
+      <c r="F212" s="8">
         <v>75964</v>
       </c>
-      <c r="G212" s="9">
+      <c r="G212" s="8">
         <v>0</v>
       </c>
-      <c r="H212" s="9">
+      <c r="H212" s="8">
         <v>10</v>
       </c>
     </row>
@@ -13704,16 +13716,16 @@
       <c r="D213" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E213" s="9">
+      <c r="E213" s="8">
         <v>6580</v>
       </c>
-      <c r="F213" s="9">
+      <c r="F213" s="8">
         <v>1432883</v>
       </c>
-      <c r="G213" s="9">
+      <c r="G213" s="8">
         <v>29</v>
       </c>
-      <c r="H213" s="9">
+      <c r="H213" s="8">
         <v>145</v>
       </c>
     </row>
@@ -13730,16 +13742,16 @@
       <c r="D214" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E214" s="9">
+      <c r="E214" s="8">
         <v>11</v>
       </c>
-      <c r="F214" s="9">
+      <c r="F214" s="8">
         <v>6036</v>
       </c>
-      <c r="G214" s="9">
+      <c r="G214" s="8">
         <v>0</v>
       </c>
-      <c r="H214" s="9">
+      <c r="H214" s="8">
         <v>2</v>
       </c>
     </row>
@@ -13756,16 +13768,16 @@
       <c r="D215" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E215" s="9">
+      <c r="E215" s="8">
         <v>4253</v>
       </c>
-      <c r="F215" s="9">
+      <c r="F215" s="8">
         <v>3784694</v>
       </c>
-      <c r="G215" s="9">
+      <c r="G215" s="8">
         <v>6</v>
       </c>
-      <c r="H215" s="9">
+      <c r="H215" s="8">
         <v>10</v>
       </c>
     </row>
@@ -13782,16 +13794,16 @@
       <c r="D216" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E216" s="9">
+      <c r="E216" s="8">
         <v>67</v>
       </c>
-      <c r="F216" s="9">
+      <c r="F216" s="8">
         <v>5</v>
       </c>
-      <c r="G216" s="9">
+      <c r="G216" s="8">
         <v>0</v>
       </c>
-      <c r="H216" s="9">
+      <c r="H216" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13808,16 +13820,16 @@
       <c r="D217" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E217" s="9">
+      <c r="E217" s="8">
         <v>4961</v>
       </c>
-      <c r="F217" s="9">
+      <c r="F217" s="8">
         <v>1388657</v>
       </c>
-      <c r="G217" s="9">
+      <c r="G217" s="8">
         <v>2</v>
       </c>
-      <c r="H217" s="9">
+      <c r="H217" s="8">
         <v>6</v>
       </c>
     </row>
@@ -13834,16 +13846,16 @@
       <c r="D218" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E218" s="9">
+      <c r="E218" s="8">
         <v>1</v>
       </c>
-      <c r="F218" s="9">
+      <c r="F218" s="8">
         <v>1</v>
       </c>
-      <c r="G218" s="9">
+      <c r="G218" s="8">
         <v>0</v>
       </c>
-      <c r="H218" s="9">
+      <c r="H218" s="8">
         <v>0</v>
       </c>
     </row>
@@ -13860,16 +13872,16 @@
       <c r="D219" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E219" s="9">
+      <c r="E219" s="8">
         <v>6121</v>
       </c>
-      <c r="F219" s="9">
+      <c r="F219" s="8">
         <v>3080470</v>
       </c>
-      <c r="G219" s="9">
+      <c r="G219" s="8">
         <v>20</v>
       </c>
-      <c r="H219" s="9">
+      <c r="H219" s="8">
         <v>22</v>
       </c>
     </row>
@@ -13886,16 +13898,16 @@
       <c r="D220" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E220" s="9">
+      <c r="E220" s="8">
         <v>243</v>
       </c>
-      <c r="F220" s="9">
+      <c r="F220" s="8">
         <v>17036</v>
       </c>
-      <c r="G220" s="9">
+      <c r="G220" s="8">
         <v>0</v>
       </c>
-      <c r="H220" s="9">
+      <c r="H220" s="8">
         <v>2</v>
       </c>
     </row>
@@ -13912,16 +13924,16 @@
       <c r="D221" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E221" s="9">
+      <c r="E221" s="8">
         <v>9729</v>
       </c>
-      <c r="F221" s="9">
+      <c r="F221" s="8">
         <v>15561853</v>
       </c>
-      <c r="G221" s="9">
+      <c r="G221" s="8">
         <v>674</v>
       </c>
-      <c r="H221" s="9">
+      <c r="H221" s="8">
         <v>827</v>
       </c>
     </row>
@@ -13938,16 +13950,16 @@
       <c r="D222" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E222" s="9">
+      <c r="E222" s="8">
         <v>154</v>
       </c>
-      <c r="F222" s="9">
+      <c r="F222" s="8">
         <v>8762</v>
       </c>
-      <c r="G222" s="9">
+      <c r="G222" s="8">
         <v>0</v>
       </c>
-      <c r="H222" s="9">
+      <c r="H222" s="8">
         <v>30</v>
       </c>
     </row>
@@ -13964,16 +13976,16 @@
       <c r="D223" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E223" s="9">
+      <c r="E223" s="8">
         <v>1313</v>
       </c>
-      <c r="F223" s="9">
+      <c r="F223" s="8">
         <v>362974</v>
       </c>
-      <c r="G223" s="9">
+      <c r="G223" s="8">
         <v>5</v>
       </c>
-      <c r="H223" s="9">
+      <c r="H223" s="8">
         <v>17</v>
       </c>
     </row>
@@ -13990,16 +14002,16 @@
       <c r="D224" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E224" s="9">
+      <c r="E224" s="8">
         <v>23</v>
       </c>
-      <c r="F224" s="9">
+      <c r="F224" s="8">
         <v>597</v>
       </c>
-      <c r="G224" s="9">
+      <c r="G224" s="8">
         <v>0</v>
       </c>
-      <c r="H224" s="9">
+      <c r="H224" s="8">
         <v>4</v>
       </c>
     </row>
@@ -14016,16 +14028,16 @@
       <c r="D225" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E225" s="9">
+      <c r="E225" s="8">
         <v>3018</v>
       </c>
-      <c r="F225" s="9">
+      <c r="F225" s="8">
         <v>2268437</v>
       </c>
-      <c r="G225" s="9">
+      <c r="G225" s="8">
         <v>33</v>
       </c>
-      <c r="H225" s="9">
+      <c r="H225" s="8">
         <v>47</v>
       </c>
     </row>
@@ -14042,16 +14054,16 @@
       <c r="D226" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E226" s="9">
+      <c r="E226" s="8">
         <v>117</v>
       </c>
-      <c r="F226" s="9">
+      <c r="F226" s="8">
         <v>5059</v>
       </c>
-      <c r="G226" s="9">
+      <c r="G226" s="8">
         <v>0</v>
       </c>
-      <c r="H226" s="9">
+      <c r="H226" s="8">
         <v>12</v>
       </c>
     </row>
@@ -14068,16 +14080,16 @@
       <c r="D227" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E227" s="9">
+      <c r="E227" s="8">
         <v>1600</v>
       </c>
-      <c r="F227" s="9">
+      <c r="F227" s="8">
         <v>5728615</v>
       </c>
-      <c r="G227" s="9">
+      <c r="G227" s="8">
         <v>31</v>
       </c>
-      <c r="H227" s="9">
+      <c r="H227" s="8">
         <v>76</v>
       </c>
     </row>
@@ -14094,16 +14106,16 @@
       <c r="D228" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E228" s="9">
+      <c r="E228" s="8">
         <v>5</v>
       </c>
-      <c r="F228" s="9">
+      <c r="F228" s="8">
         <v>8126</v>
       </c>
-      <c r="G228" s="9">
+      <c r="G228" s="8">
         <v>0</v>
       </c>
-      <c r="H228" s="9">
+      <c r="H228" s="8">
         <v>3</v>
       </c>
     </row>
@@ -14120,16 +14132,16 @@
       <c r="D229" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E229" s="9">
+      <c r="E229" s="8">
         <v>8085</v>
       </c>
-      <c r="F229" s="9">
+      <c r="F229" s="8">
         <v>76954323</v>
       </c>
-      <c r="G229" s="9">
+      <c r="G229" s="8">
         <v>183</v>
       </c>
-      <c r="H229" s="9">
+      <c r="H229" s="8">
         <v>199</v>
       </c>
     </row>
@@ -14146,16 +14158,16 @@
       <c r="D230" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E230" s="9">
+      <c r="E230" s="8">
         <v>108</v>
       </c>
-      <c r="F230" s="9">
+      <c r="F230" s="8">
         <v>49</v>
       </c>
-      <c r="G230" s="9">
+      <c r="G230" s="8">
         <v>0</v>
       </c>
-      <c r="H230" s="9">
+      <c r="H230" s="8">
         <v>3</v>
       </c>
     </row>
@@ -14172,16 +14184,16 @@
       <c r="D231" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E231" s="9">
+      <c r="E231" s="8">
         <v>5089</v>
       </c>
-      <c r="F231" s="9">
+      <c r="F231" s="8">
         <v>1802549</v>
       </c>
-      <c r="G231" s="9">
+      <c r="G231" s="8">
         <v>112</v>
       </c>
-      <c r="H231" s="9">
+      <c r="H231" s="8">
         <v>139</v>
       </c>
     </row>
@@ -14198,16 +14210,16 @@
       <c r="D232" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E232" s="9">
+      <c r="E232" s="8">
         <v>297</v>
       </c>
-      <c r="F232" s="9">
+      <c r="F232" s="8">
         <v>26131</v>
       </c>
-      <c r="G232" s="9">
+      <c r="G232" s="8">
         <v>0</v>
       </c>
-      <c r="H232" s="9">
+      <c r="H232" s="8">
         <v>4</v>
       </c>
     </row>
@@ -14224,16 +14236,16 @@
       <c r="D233" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E233" s="9">
+      <c r="E233" s="8">
         <v>7781</v>
       </c>
-      <c r="F233" s="9">
+      <c r="F233" s="8">
         <v>86553082</v>
       </c>
-      <c r="G233" s="9">
+      <c r="G233" s="8">
         <v>240</v>
       </c>
-      <c r="H233" s="9">
+      <c r="H233" s="8">
         <v>430</v>
       </c>
     </row>
@@ -14250,16 +14262,16 @@
       <c r="D234" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E234" s="9">
+      <c r="E234" s="8">
         <v>403</v>
       </c>
-      <c r="F234" s="9">
+      <c r="F234" s="8">
         <v>66945</v>
       </c>
-      <c r="G234" s="9">
+      <c r="G234" s="8">
         <v>0</v>
       </c>
-      <c r="H234" s="9">
+      <c r="H234" s="8">
         <v>37</v>
       </c>
     </row>
@@ -14276,16 +14288,16 @@
       <c r="D235" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E235" s="9">
+      <c r="E235" s="8">
         <v>580</v>
       </c>
-      <c r="F235" s="9">
+      <c r="F235" s="8">
         <v>1675853</v>
       </c>
-      <c r="G235" s="9">
+      <c r="G235" s="8">
         <v>12</v>
       </c>
-      <c r="H235" s="9">
+      <c r="H235" s="8">
         <v>43</v>
       </c>
     </row>
@@ -14302,16 +14314,16 @@
       <c r="D236" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E236" s="9">
+      <c r="E236" s="8">
         <v>5</v>
       </c>
-      <c r="F236" s="9">
+      <c r="F236" s="8">
         <v>123</v>
       </c>
-      <c r="G236" s="9">
+      <c r="G236" s="8">
         <v>0</v>
       </c>
-      <c r="H236" s="9">
+      <c r="H236" s="8">
         <v>3</v>
       </c>
     </row>
@@ -14328,16 +14340,16 @@
       <c r="D237" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E237" s="9">
+      <c r="E237" s="8">
         <v>10627</v>
       </c>
-      <c r="F237" s="9">
+      <c r="F237" s="8">
         <v>15516425</v>
       </c>
-      <c r="G237" s="9">
+      <c r="G237" s="8">
         <v>133</v>
       </c>
-      <c r="H237" s="9">
+      <c r="H237" s="8">
         <v>161</v>
       </c>
     </row>
@@ -14354,16 +14366,16 @@
       <c r="D238" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E238" s="9">
+      <c r="E238" s="8">
         <v>290</v>
       </c>
-      <c r="F238" s="9">
+      <c r="F238" s="8">
         <v>5867</v>
       </c>
-      <c r="G238" s="9">
+      <c r="G238" s="8">
         <v>0</v>
       </c>
-      <c r="H238" s="9">
+      <c r="H238" s="8">
         <v>8</v>
       </c>
     </row>
@@ -14380,16 +14392,16 @@
       <c r="D239" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E239" s="9">
+      <c r="E239" s="8">
         <v>1540</v>
       </c>
-      <c r="F239" s="9">
+      <c r="F239" s="8">
         <v>15557629</v>
       </c>
-      <c r="G239" s="9">
+      <c r="G239" s="8">
         <v>10</v>
       </c>
-      <c r="H239" s="9">
+      <c r="H239" s="8">
         <v>20</v>
       </c>
     </row>
@@ -14406,16 +14418,16 @@
       <c r="D240" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E240" s="9">
+      <c r="E240" s="8">
         <v>2</v>
       </c>
-      <c r="F240" s="9">
+      <c r="F240" s="8">
         <v>2</v>
       </c>
-      <c r="G240" s="9">
+      <c r="G240" s="8">
         <v>0</v>
       </c>
-      <c r="H240" s="9">
+      <c r="H240" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14432,16 +14444,16 @@
       <c r="D241" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E241" s="9">
+      <c r="E241" s="8">
         <v>8909</v>
       </c>
-      <c r="F241" s="9">
+      <c r="F241" s="8">
         <v>3833085</v>
       </c>
-      <c r="G241" s="9">
+      <c r="G241" s="8">
         <v>65</v>
       </c>
-      <c r="H241" s="9">
+      <c r="H241" s="8">
         <v>79</v>
       </c>
     </row>
@@ -14458,16 +14470,16 @@
       <c r="D242" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E242" s="9">
+      <c r="E242" s="8">
         <v>106</v>
       </c>
-      <c r="F242" s="9">
+      <c r="F242" s="8">
         <v>477</v>
       </c>
-      <c r="G242" s="9">
+      <c r="G242" s="8">
         <v>0</v>
       </c>
-      <c r="H242" s="9">
+      <c r="H242" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14484,16 +14496,16 @@
       <c r="D243" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E243" s="9">
+      <c r="E243" s="8">
         <v>1824</v>
       </c>
-      <c r="F243" s="9">
+      <c r="F243" s="8">
         <v>29321694</v>
       </c>
-      <c r="G243" s="9">
+      <c r="G243" s="8">
         <v>41</v>
       </c>
-      <c r="H243" s="9">
+      <c r="H243" s="8">
         <v>47</v>
       </c>
     </row>
@@ -14510,16 +14522,16 @@
       <c r="D244" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E244" s="9">
+      <c r="E244" s="8">
         <v>109</v>
       </c>
-      <c r="F244" s="9">
+      <c r="F244" s="8">
         <v>2909</v>
       </c>
-      <c r="G244" s="9">
+      <c r="G244" s="8">
         <v>0</v>
       </c>
-      <c r="H244" s="9">
+      <c r="H244" s="8">
         <v>4</v>
       </c>
     </row>
@@ -14536,16 +14548,16 @@
       <c r="D245" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E245" s="9">
+      <c r="E245" s="8">
         <v>1</v>
       </c>
-      <c r="F245" s="9">
+      <c r="F245" s="8">
         <v>13072</v>
       </c>
-      <c r="G245" s="9">
+      <c r="G245" s="8">
         <v>0</v>
       </c>
-      <c r="H245" s="9">
+      <c r="H245" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14562,16 +14574,16 @@
       <c r="D246" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E246" s="9">
+      <c r="E246" s="8">
         <v>6537</v>
       </c>
-      <c r="F246" s="9">
+      <c r="F246" s="8">
         <v>1415946</v>
       </c>
-      <c r="G246" s="9">
+      <c r="G246" s="8">
         <v>27</v>
       </c>
-      <c r="H246" s="9">
+      <c r="H246" s="8">
         <v>37</v>
       </c>
     </row>
@@ -14588,16 +14600,16 @@
       <c r="D247" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E247" s="9">
+      <c r="E247" s="8">
         <v>2</v>
       </c>
-      <c r="F247" s="9">
+      <c r="F247" s="8">
         <v>30</v>
       </c>
-      <c r="G247" s="9">
+      <c r="G247" s="8">
         <v>0</v>
       </c>
-      <c r="H247" s="9">
+      <c r="H247" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14614,16 +14626,16 @@
       <c r="D248" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E248" s="9">
+      <c r="E248" s="8">
         <v>3055</v>
       </c>
-      <c r="F248" s="9">
+      <c r="F248" s="8">
         <v>49313209</v>
       </c>
-      <c r="G248" s="9">
+      <c r="G248" s="8">
         <v>132</v>
       </c>
-      <c r="H248" s="9">
+      <c r="H248" s="8">
         <v>159</v>
       </c>
     </row>
@@ -14640,16 +14652,16 @@
       <c r="D249" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E249" s="9">
+      <c r="E249" s="8">
         <v>350</v>
       </c>
-      <c r="F249" s="9">
+      <c r="F249" s="8">
         <v>4699</v>
       </c>
-      <c r="G249" s="9">
+      <c r="G249" s="8">
         <v>0</v>
       </c>
-      <c r="H249" s="9">
+      <c r="H249" s="8">
         <v>19</v>
       </c>
     </row>
@@ -14666,16 +14678,16 @@
       <c r="D250" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E250" s="9">
+      <c r="E250" s="8">
         <v>8565</v>
       </c>
-      <c r="F250" s="9">
+      <c r="F250" s="8">
         <v>6614126</v>
       </c>
-      <c r="G250" s="9">
+      <c r="G250" s="8">
         <v>288</v>
       </c>
-      <c r="H250" s="9">
+      <c r="H250" s="8">
         <v>344</v>
       </c>
     </row>
@@ -14692,16 +14704,16 @@
       <c r="D251" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E251" s="9">
+      <c r="E251" s="8">
         <v>531</v>
       </c>
-      <c r="F251" s="9">
+      <c r="F251" s="8">
         <v>141816</v>
       </c>
-      <c r="G251" s="9">
+      <c r="G251" s="8">
         <v>0</v>
       </c>
-      <c r="H251" s="9">
+      <c r="H251" s="8">
         <v>23</v>
       </c>
     </row>
@@ -14718,16 +14730,16 @@
       <c r="D252" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E252" s="9">
+      <c r="E252" s="8">
         <v>6665</v>
       </c>
-      <c r="F252" s="9">
+      <c r="F252" s="8">
         <v>43632104</v>
       </c>
-      <c r="G252" s="9">
+      <c r="G252" s="8">
         <v>165</v>
       </c>
-      <c r="H252" s="9">
+      <c r="H252" s="8">
         <v>183</v>
       </c>
     </row>
@@ -14744,16 +14756,16 @@
       <c r="D253" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E253" s="9">
+      <c r="E253" s="8">
         <v>172</v>
       </c>
-      <c r="F253" s="9">
+      <c r="F253" s="8">
         <v>362630</v>
       </c>
-      <c r="G253" s="9">
+      <c r="G253" s="8">
         <v>0</v>
       </c>
-      <c r="H253" s="9">
+      <c r="H253" s="8">
         <v>13</v>
       </c>
     </row>
@@ -14770,16 +14782,16 @@
       <c r="D254" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E254" s="9">
+      <c r="E254" s="8">
         <v>2831</v>
       </c>
-      <c r="F254" s="9">
+      <c r="F254" s="8">
         <v>999822</v>
       </c>
-      <c r="G254" s="9">
+      <c r="G254" s="8">
         <v>43</v>
       </c>
-      <c r="H254" s="9">
+      <c r="H254" s="8">
         <v>48</v>
       </c>
     </row>
@@ -14796,16 +14808,16 @@
       <c r="D255" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E255" s="9">
+      <c r="E255" s="8">
         <v>113</v>
       </c>
-      <c r="F255" s="9">
+      <c r="F255" s="8">
         <v>53</v>
       </c>
-      <c r="G255" s="9">
+      <c r="G255" s="8">
         <v>0</v>
       </c>
-      <c r="H255" s="9">
+      <c r="H255" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14822,16 +14834,16 @@
       <c r="D256" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E256" s="9">
+      <c r="E256" s="8">
         <v>10359</v>
       </c>
-      <c r="F256" s="9">
+      <c r="F256" s="8">
         <v>2255568</v>
       </c>
-      <c r="G256" s="9">
+      <c r="G256" s="8">
         <v>105</v>
       </c>
-      <c r="H256" s="9">
+      <c r="H256" s="8">
         <v>165</v>
       </c>
     </row>
@@ -14848,16 +14860,16 @@
       <c r="D257" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E257" s="9">
+      <c r="E257" s="8">
         <v>3</v>
       </c>
-      <c r="F257" s="9">
+      <c r="F257" s="8">
         <v>3</v>
       </c>
-      <c r="G257" s="9">
+      <c r="G257" s="8">
         <v>0</v>
       </c>
-      <c r="H257" s="9">
+      <c r="H257" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14874,16 +14886,16 @@
       <c r="D258" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E258" s="9">
+      <c r="E258" s="8">
         <v>189</v>
       </c>
-      <c r="F258" s="9">
+      <c r="F258" s="8">
         <v>578727</v>
       </c>
-      <c r="G258" s="9">
+      <c r="G258" s="8">
         <v>1</v>
       </c>
-      <c r="H258" s="9">
+      <c r="H258" s="8">
         <v>173</v>
       </c>
     </row>
@@ -14900,16 +14912,16 @@
       <c r="D259" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E259" s="9">
+      <c r="E259" s="8">
         <v>36</v>
       </c>
-      <c r="F259" s="9">
+      <c r="F259" s="8">
         <v>16</v>
       </c>
-      <c r="G259" s="9">
+      <c r="G259" s="8">
         <v>0</v>
       </c>
-      <c r="H259" s="9">
+      <c r="H259" s="8">
         <v>3</v>
       </c>
     </row>
@@ -14926,16 +14938,16 @@
       <c r="D260" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E260" s="9">
+      <c r="E260" s="8">
         <v>51</v>
       </c>
-      <c r="F260" s="9">
+      <c r="F260" s="8">
         <v>168550</v>
       </c>
-      <c r="G260" s="9">
+      <c r="G260" s="8">
         <v>0</v>
       </c>
-      <c r="H260" s="9">
+      <c r="H260" s="8">
         <v>50</v>
       </c>
     </row>
@@ -14952,16 +14964,16 @@
       <c r="D261" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E261" s="9">
+      <c r="E261" s="8">
         <v>4</v>
       </c>
-      <c r="F261" s="9">
+      <c r="F261" s="8">
         <v>4629</v>
       </c>
-      <c r="G261" s="9">
+      <c r="G261" s="8">
         <v>0</v>
       </c>
-      <c r="H261" s="9">
+      <c r="H261" s="8">
         <v>0</v>
       </c>
     </row>
@@ -14978,16 +14990,16 @@
       <c r="D262" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E262" s="9">
+      <c r="E262" s="8">
         <v>229</v>
       </c>
-      <c r="F262" s="9">
+      <c r="F262" s="8">
         <v>3555943</v>
       </c>
-      <c r="G262" s="9">
+      <c r="G262" s="8">
         <v>1</v>
       </c>
-      <c r="H262" s="9">
+      <c r="H262" s="8">
         <v>2</v>
       </c>
     </row>
@@ -15004,16 +15016,16 @@
       <c r="D263" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E263" s="9">
+      <c r="E263" s="8">
         <v>17</v>
       </c>
-      <c r="F263" s="9">
+      <c r="F263" s="8">
         <v>17333</v>
       </c>
-      <c r="G263" s="9">
+      <c r="G263" s="8">
         <v>0</v>
       </c>
-      <c r="H263" s="9">
+      <c r="H263" s="8">
         <v>5</v>
       </c>
     </row>
@@ -15030,16 +15042,16 @@
       <c r="D264" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E264" s="9">
+      <c r="E264" s="8">
         <v>17</v>
       </c>
-      <c r="F264" s="9">
+      <c r="F264" s="8">
         <v>21560</v>
       </c>
-      <c r="G264" s="9">
+      <c r="G264" s="8">
         <v>0</v>
       </c>
-      <c r="H264" s="9">
+      <c r="H264" s="8">
         <v>1</v>
       </c>
     </row>
@@ -15056,16 +15068,16 @@
       <c r="D265" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E265" s="9">
+      <c r="E265" s="8">
         <v>19</v>
       </c>
-      <c r="F265" s="9">
+      <c r="F265" s="8">
         <v>320</v>
       </c>
-      <c r="G265" s="9">
+      <c r="G265" s="8">
         <v>0</v>
       </c>
-      <c r="H265" s="9">
+      <c r="H265" s="8">
         <v>4</v>
       </c>
     </row>
@@ -15082,16 +15094,16 @@
       <c r="D266" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E266" s="9">
+      <c r="E266" s="8">
         <v>4093</v>
       </c>
-      <c r="F266" s="9">
+      <c r="F266" s="8">
         <v>777718</v>
       </c>
-      <c r="G266" s="9">
+      <c r="G266" s="8">
         <v>41</v>
       </c>
-      <c r="H266" s="9">
+      <c r="H266" s="8">
         <v>77</v>
       </c>
     </row>
@@ -15108,16 +15120,16 @@
       <c r="D267" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E267" s="9">
+      <c r="E267" s="8">
         <v>40</v>
       </c>
-      <c r="F267" s="9">
+      <c r="F267" s="8">
         <v>255</v>
       </c>
-      <c r="G267" s="9">
+      <c r="G267" s="8">
         <v>0</v>
       </c>
-      <c r="H267" s="9">
+      <c r="H267" s="8">
         <v>2</v>
       </c>
     </row>
@@ -15134,16 +15146,16 @@
       <c r="D268" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E268" s="9">
+      <c r="E268" s="8">
         <v>4</v>
       </c>
-      <c r="F268" s="9">
+      <c r="F268" s="8">
         <v>28639</v>
       </c>
-      <c r="G268" s="9">
+      <c r="G268" s="8">
         <v>0</v>
       </c>
-      <c r="H268" s="9">
+      <c r="H268" s="8">
         <v>0</v>
       </c>
     </row>
@@ -15160,16 +15172,16 @@
       <c r="D269" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E269" s="9">
+      <c r="E269" s="8">
         <v>6</v>
       </c>
-      <c r="F269" s="9">
+      <c r="F269" s="8">
         <v>1875473</v>
       </c>
-      <c r="G269" s="9">
+      <c r="G269" s="8">
         <v>0</v>
       </c>
-      <c r="H269" s="9">
+      <c r="H269" s="8">
         <v>1</v>
       </c>
     </row>
@@ -15186,16 +15198,16 @@
       <c r="D270" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E270" s="9">
+      <c r="E270" s="8">
         <v>14</v>
       </c>
-      <c r="F270" s="9">
+      <c r="F270" s="8">
         <v>528</v>
       </c>
-      <c r="G270" s="9">
+      <c r="G270" s="8">
         <v>0</v>
       </c>
-      <c r="H270" s="9">
+      <c r="H270" s="8">
         <v>0</v>
       </c>
     </row>
@@ -15212,16 +15224,16 @@
       <c r="D271" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E271" s="9">
+      <c r="E271" s="8">
         <v>40</v>
       </c>
-      <c r="F271" s="9">
+      <c r="F271" s="8">
         <v>1146</v>
       </c>
-      <c r="G271" s="9">
+      <c r="G271" s="8">
         <v>2</v>
       </c>
-      <c r="H271" s="9">
+      <c r="H271" s="8">
         <v>5</v>
       </c>
     </row>
@@ -15238,16 +15250,16 @@
       <c r="D272" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E272" s="9">
+      <c r="E272" s="8">
         <v>36</v>
       </c>
-      <c r="F272" s="9">
+      <c r="F272" s="8">
         <v>7272</v>
       </c>
-      <c r="G272" s="9">
+      <c r="G272" s="8">
         <v>0</v>
       </c>
-      <c r="H272" s="9">
+      <c r="H272" s="8">
         <v>0</v>
       </c>
     </row>
@@ -15264,16 +15276,16 @@
       <c r="D273" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E273" s="9">
+      <c r="E273" s="8">
         <v>6226</v>
       </c>
-      <c r="F273" s="9">
+      <c r="F273" s="8">
         <v>137907551</v>
       </c>
-      <c r="G273" s="9">
+      <c r="G273" s="8">
         <v>25</v>
       </c>
-      <c r="H273" s="9">
+      <c r="H273" s="8">
         <v>53</v>
       </c>
     </row>
@@ -15290,16 +15302,16 @@
       <c r="D274" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E274" s="9">
+      <c r="E274" s="8">
         <v>39</v>
       </c>
-      <c r="F274" s="9">
+      <c r="F274" s="8">
         <v>1883</v>
       </c>
-      <c r="G274" s="9">
+      <c r="G274" s="8">
         <v>0</v>
       </c>
-      <c r="H274" s="9">
+      <c r="H274" s="8">
         <v>11</v>
       </c>
     </row>
@@ -15316,16 +15328,16 @@
       <c r="D275" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E275" s="9">
+      <c r="E275" s="8">
         <v>2</v>
       </c>
-      <c r="F275" s="9">
+      <c r="F275" s="8">
         <v>28</v>
       </c>
-      <c r="G275" s="9">
+      <c r="G275" s="8">
         <v>0</v>
       </c>
-      <c r="H275" s="9">
+      <c r="H275" s="8">
         <v>0</v>
       </c>
     </row>
@@ -37733,11 +37745,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" sqref="G2 G3 G4 G9 G10 G11 G14 G15 G16 G19 G20 G21 G22 G23 G24 G25 G26 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G47 G48 G49 G50 G51 G52 G55 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G78 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G101 G102 G103 G104 G105 G108 G109 G110 G111 G112 G113 G114 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G190 G191 G192 G193 G197 G198 G199 G200 G201 G202 G203 G204 G205 G206 G207 G208 G209 G5:G6 G7:G8 G12:G13 G17:G18 G27:G28 G45:G46 G53:G54 G56:G57 G76:G77 G79:G80 G81:G82 G99:G100 G106:G107 G115:G116 G130:G131 G132:G134 G165:G166 G188:G189 G194:G196">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" sqref="G2:G209">
       <formula1>-999999999999.99</formula1>
       <formula2>999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请从下拉项中选择" sqref="AH2 AH3 AH4 AH9 AH10 AH11 AH14 AH15 AH16 AH19 AH20 AH21 AH22 AH23 AH24 AH25 AH26 AH29 AH30 AH31 AH32 AH33 AH34 AH35 AH36 AH37 AH38 AH39 AH40 AH41 AH42 AH43 AH44 AH47 AH48 AH49 AH50 AH51 AH52 AH55 AH58 AH59 AH60 AH61 AH62 AH63 AH64 AH65 AH66 AH67 AH68 AH69 AH70 AH71 AH72 AH73 AH74 AH75 AH78 AH83 AH84 AH85 AH86 AH87 AH88 AH89 AH90 AH91 AH92 AH93 AH94 AH95 AH96 AH97 AH98 AH101 AH102 AH103 AH104 AH105 AH108 AH109 AH110 AH111 AH112 AH113 AH114 AH117 AH118 AH119 AH120 AH121 AH122 AH123 AH124 AH125 AH126 AH127 AH128 AH129 AH135 AH136 AH137 AH138 AH139 AH140 AH141 AH142 AH143 AH144 AH145 AH146 AH147 AH148 AH149 AH150 AH151 AH152 AH153 AH154 AH155 AH156 AH157 AH158 AH159 AH160 AH161 AH162 AH163 AH164 AH167 AH168 AH169 AH170 AH171 AH172 AH173 AH174 AH175 AH176 AH177 AH178 AH179 AH180 AH181 AH182 AH183 AH184 AH185 AH186 AH187 AH190 AH191 AH192 AH193 AH197 AH198 AH199 AH200 AH201 AH202 AH203 AH204 AH205 AH206 AH207 AH208 AH209 AH5:AH6 AH7:AH8 AH12:AH13 AH17:AH18 AH27:AH28 AH45:AH46 AH53:AH54 AH56:AH57 AH76:AH77 AH79:AH80 AH81:AH82 AH99:AH100 AH106:AH107 AH115:AH116 AH130:AH131 AH132:AH134 AH165:AH166 AH188:AH189 AH194:AH196">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请从下拉项中选择" sqref="AH2:AH209">
       <formula1>StatusOptions_33</formula1>
     </dataValidation>
   </dataValidations>
